--- a/data-source/ESTOQUEQUIMICOS.xlsx
+++ b/data-source/ESTOQUEQUIMICOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{456BA992-3F33-4626-9BFC-A94C96A28811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0BE9B2B-B0F1-4DD7-A016-1671161FFF73}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{456BA992-3F33-4626-9BFC-A94C96A28811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED85D5C-6219-4A4F-A2A9-F47407B1B4FB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$E$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha!$A$1:$E$205</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Planilha!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="204">
   <si>
     <t>Produto</t>
   </si>
@@ -522,9 +522,6 @@
     <t>RESINA MJ9640 - AMERICA ASIA</t>
   </si>
   <si>
-    <t>RESINA LR206 (AMERICA ASIA)</t>
-  </si>
-  <si>
     <t>RESINA LR-8372H (AMERICA ASIA)</t>
   </si>
   <si>
@@ -651,7 +648,7 @@
     <t>RESINA NOVOTEX - AL233</t>
   </si>
   <si>
-    <t>PIGMENTO PEROLADO AG/KW 502 RED BROWN</t>
+    <t>RESINA LR206M-3 (AMERICA ASIA)</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1057,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1084,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1101,7 +1098,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1109,7 +1106,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C3" s="4">
         <v>205</v>
@@ -1118,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1146,13 +1143,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D5" s="2">
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1169,7 +1166,7 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1177,7 +1174,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="4">
         <v>40</v>
@@ -1186,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1203,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1220,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1237,7 +1234,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1254,7 +1251,7 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1265,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>865</v>
+        <v>4337</v>
       </c>
       <c r="D12" s="2">
         <v>9</v>
@@ -1282,7 +1279,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="4">
-        <v>372</v>
+        <v>186</v>
       </c>
       <c r="D13" s="2">
         <v>9</v>
@@ -1305,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1322,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1339,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1356,7 +1353,7 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1373,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1390,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1407,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1424,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1441,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1458,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1475,7 +1472,7 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1492,7 +1489,7 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1509,7 +1506,7 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1526,7 +1523,7 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1543,7 +1540,7 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1560,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1577,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1594,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1611,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1628,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1645,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1662,7 +1659,7 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1679,7 +1676,7 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1696,7 +1693,7 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1713,7 +1710,7 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1730,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1747,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1764,7 +1761,7 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1781,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1798,7 +1795,7 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1815,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1826,13 +1823,13 @@
         <v>46</v>
       </c>
       <c r="C45" s="4">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="D45" s="2">
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1849,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1866,7 +1863,7 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1877,13 +1874,13 @@
         <v>49</v>
       </c>
       <c r="C48" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D48" s="2">
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1900,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1917,7 +1914,7 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1934,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1951,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1962,13 +1959,13 @@
         <v>54</v>
       </c>
       <c r="C53" s="4">
-        <v>939</v>
+        <v>769</v>
       </c>
       <c r="D53" s="2">
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1985,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2002,7 +1999,7 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2019,7 +2016,7 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2044,10 +2041,10 @@
         <v>135</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C58" s="4">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="D58" s="2">
         <v>9</v>
@@ -2121,7 +2118,7 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2138,7 +2135,7 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2155,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2189,7 +2186,7 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2206,7 +2203,7 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2223,7 +2220,7 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2240,7 +2237,7 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2257,7 +2254,7 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2274,7 +2271,7 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2291,7 +2288,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2308,7 +2305,7 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2325,7 +2322,7 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2342,7 +2339,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2359,7 +2356,7 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2376,7 +2373,7 @@
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2393,7 +2390,7 @@
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2410,7 +2407,7 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2427,7 +2424,7 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2444,7 +2441,7 @@
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2461,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2478,7 +2475,7 @@
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2495,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2512,7 +2509,7 @@
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2529,7 +2526,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2563,7 +2560,7 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2580,7 +2577,7 @@
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2597,7 +2594,7 @@
         <v>9</v>
       </c>
       <c r="E90" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2614,7 +2611,7 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2631,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2648,7 +2645,7 @@
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2665,7 +2662,7 @@
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2682,7 +2679,7 @@
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2699,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2716,7 +2713,7 @@
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2733,7 +2730,7 @@
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2750,7 +2747,7 @@
         <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2767,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2784,7 +2781,7 @@
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2801,7 +2798,7 @@
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2818,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2852,7 +2849,7 @@
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2869,7 +2866,7 @@
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2880,13 +2877,13 @@
         <v>107</v>
       </c>
       <c r="C107" s="4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D107" s="2">
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2903,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2920,7 +2917,7 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2937,7 +2934,7 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -2954,7 +2951,7 @@
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -2971,7 +2968,7 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2988,7 +2985,7 @@
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2999,13 +2996,13 @@
         <v>114</v>
       </c>
       <c r="C114" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D114" s="2">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3022,7 +3019,7 @@
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3039,7 +3036,7 @@
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3056,7 +3053,7 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3073,7 +3070,7 @@
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -3090,7 +3087,7 @@
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3107,7 +3104,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3124,7 +3121,7 @@
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3132,7 +3129,7 @@
         <v>5087</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C122" s="4">
         <v>25</v>
@@ -3141,7 +3138,7 @@
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3158,83 +3155,83 @@
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>5120</v>
+        <v>5187</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="C124" s="4">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="D124" s="2">
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>5187</v>
+        <v>5260</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C125" s="4">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="D125" s="2">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>5260</v>
+        <v>5373</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C126" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D126" s="2">
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>5373</v>
+        <v>5736</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C127" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D127" s="2">
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>5736</v>
+        <v>5741</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C128" s="4">
         <v>5</v>
@@ -3243,109 +3240,109 @@
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>190</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C129" s="4">
-        <v>5</v>
+        <v>19.2</v>
       </c>
       <c r="D129" s="2">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C130" s="4">
-        <v>19.2</v>
+        <v>2</v>
       </c>
       <c r="D130" s="2">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>5743</v>
+        <v>5747</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C131" s="4">
-        <v>2</v>
+        <v>5.98</v>
       </c>
       <c r="D131" s="2">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C132" s="4">
-        <v>5.98</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D132" s="2">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>5748</v>
+        <v>5750</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C133" s="4">
-        <v>4.5999999999999996</v>
+        <v>28.7</v>
       </c>
       <c r="D133" s="2">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>5750</v>
+        <v>5796</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C134" s="4">
-        <v>28.7</v>
+        <v>50</v>
       </c>
       <c r="D134" s="2">
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3356,449 +3353,449 @@
         <v>132</v>
       </c>
       <c r="C135" s="4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D135" s="2">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C136" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D136" s="2">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>5797</v>
+        <v>5809</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C137" s="4">
-        <v>100</v>
+        <v>359.4</v>
       </c>
       <c r="D137" s="2">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>5797</v>
+        <v>5810</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C138" s="4">
-        <v>400</v>
+        <v>1260</v>
       </c>
       <c r="D138" s="2">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>5809</v>
+        <v>5811</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C139" s="4">
-        <v>359.4</v>
+        <v>160.30000000000001</v>
       </c>
       <c r="D139" s="2">
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>5810</v>
+        <v>5812</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C140" s="4">
-        <v>1260</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="D140" s="2">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>5811</v>
+        <v>5856</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C141" s="4">
-        <v>160.30000000000001</v>
+        <v>110</v>
       </c>
       <c r="D141" s="2">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>5812</v>
+        <v>6505</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C142" s="4">
-        <v>159.80000000000001</v>
+        <v>50</v>
       </c>
       <c r="D142" s="2">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>5856</v>
+        <v>6505</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C143" s="4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D143" s="2">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C144" s="4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D144" s="2">
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C145" s="4">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="D145" s="2">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>6506</v>
+        <v>6507</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C146" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D146" s="2">
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>6506</v>
+        <v>6507</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C147" s="4">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="D147" s="2">
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>6507</v>
+        <v>6508</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C148" s="4">
-        <v>100</v>
+        <v>14.9</v>
       </c>
       <c r="D148" s="2">
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>6507</v>
+        <v>6508</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C149" s="4">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="D149" s="2">
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>6508</v>
+        <v>6509</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C150" s="4">
-        <v>14.9</v>
+        <v>82.8</v>
       </c>
       <c r="D150" s="2">
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>6508</v>
+        <v>6510</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C151" s="4">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D151" s="2">
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>6509</v>
+        <v>6510</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C152" s="4">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="D152" s="2">
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>6510</v>
+        <v>6511</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C153" s="4">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="D153" s="2">
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>6510</v>
+        <v>6512</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C154" s="4">
-        <v>100</v>
+        <v>24.998999999999999</v>
       </c>
       <c r="D154" s="2">
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>6511</v>
+        <v>6514</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C155" s="4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D155" s="2">
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>6512</v>
+        <v>6828</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C156" s="4">
-        <v>24.998999999999999</v>
+        <v>150</v>
       </c>
       <c r="D156" s="2">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>6514</v>
+        <v>8329</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C157" s="4">
-        <v>100</v>
+        <v>3800</v>
       </c>
       <c r="D157" s="2">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>6514</v>
+        <v>8894</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C158" s="4">
-        <v>250</v>
+        <v>540</v>
       </c>
       <c r="D158" s="2">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>6828</v>
+        <v>8895</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C159" s="4">
-        <v>150</v>
+        <v>36.6</v>
       </c>
       <c r="D159" s="2">
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>8329</v>
+        <v>8930</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C160" s="4">
-        <v>4750</v>
+        <v>25</v>
       </c>
       <c r="D160" s="2">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>6</v>
+        <v>197</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>8894</v>
+        <v>9716</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C161" s="4">
-        <v>540</v>
+        <v>18</v>
       </c>
       <c r="D161" s="2">
         <v>9</v>
@@ -3809,13 +3806,13 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>8895</v>
+        <v>9716</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C162" s="4">
-        <v>36.6</v>
+        <v>18</v>
       </c>
       <c r="D162" s="2">
         <v>9</v>
@@ -3826,268 +3823,268 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>8930</v>
+        <v>10497</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C163" s="4">
-        <v>25</v>
+        <v>2470</v>
       </c>
       <c r="D163" s="2">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>9716</v>
+        <v>10907</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C164" s="4">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D164" s="2">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>9716</v>
+        <v>11259</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C165" s="4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D165" s="2">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>10497</v>
+        <v>11370</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C166" s="4">
-        <v>3050</v>
+        <v>180</v>
       </c>
       <c r="D166" s="2">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>10907</v>
+        <v>11370</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C167" s="4">
-        <v>2</v>
+        <v>2700</v>
       </c>
       <c r="D167" s="2">
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>11259</v>
+        <v>11370</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C168" s="4">
-        <v>25</v>
+        <v>3960</v>
       </c>
       <c r="D168" s="2">
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>11370</v>
+        <v>11371</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C169" s="4">
-        <v>180</v>
+        <v>897</v>
       </c>
       <c r="D169" s="2">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>11370</v>
+        <v>11372</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C170" s="4">
-        <v>4500</v>
+        <v>540</v>
       </c>
       <c r="D170" s="2">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>11371</v>
+        <v>11373</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C171" s="4">
-        <v>897</v>
+        <v>705</v>
       </c>
       <c r="D171" s="2">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>11372</v>
+        <v>11374</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="C172" s="4">
-        <v>540</v>
+        <v>2160</v>
       </c>
       <c r="D172" s="2">
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>11373</v>
+        <v>11377</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C173" s="4">
-        <v>705</v>
+        <v>300</v>
       </c>
       <c r="D173" s="2">
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>11374</v>
+        <v>11377</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>161</v>
       </c>
       <c r="C174" s="4">
-        <v>2160</v>
+        <v>2700</v>
       </c>
       <c r="D174" s="2">
         <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>11377</v>
+        <v>11378</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>162</v>
       </c>
       <c r="C175" s="4">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="D175" s="2">
         <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>11377</v>
+        <v>11379</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C176" s="4">
-        <v>2700</v>
+        <v>180</v>
       </c>
       <c r="D176" s="2">
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>11378</v>
+        <v>11380</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C177" s="4">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="D177" s="2">
         <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>11379</v>
+        <v>11612</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C178" s="4">
-        <v>360</v>
+        <v>25</v>
       </c>
       <c r="D178" s="2">
         <v>9</v>
@@ -4098,78 +4095,78 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>11380</v>
+        <v>11849</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C179" s="4">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="D179" s="2">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>11612</v>
+        <v>12710</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C180" s="4">
-        <v>50</v>
+        <v>2.5</v>
       </c>
       <c r="D180" s="2">
         <v>9</v>
       </c>
       <c r="E180" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>11849</v>
+        <v>12711</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C181" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2">
         <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>12710</v>
+        <v>12712</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C182" s="4">
-        <v>2.5</v>
+        <v>0.06</v>
       </c>
       <c r="D182" s="2">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>12711</v>
+        <v>12713</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C183" s="4">
         <v>1</v>
@@ -4178,49 +4175,49 @@
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>12712</v>
+        <v>12714</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C184" s="4">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D184" s="2">
         <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>12713</v>
+        <v>12715</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C185" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D185" s="2">
         <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>12714</v>
+        <v>12716</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C186" s="4">
         <v>0.05</v>
@@ -4229,15 +4226,15 @@
         <v>9</v>
       </c>
       <c r="E186" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>12715</v>
+        <v>12717</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C187" s="4">
         <v>0.05</v>
@@ -4246,279 +4243,279 @@
         <v>9</v>
       </c>
       <c r="E187" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>12716</v>
+        <v>12718</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C188" s="4">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="D188" s="2">
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>12717</v>
+        <v>12924</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C189" s="4">
-        <v>0.05</v>
+        <v>20</v>
       </c>
       <c r="D189" s="2">
         <v>9</v>
       </c>
       <c r="E189" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>12718</v>
+        <v>14753</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C190" s="4">
-        <v>1</v>
+        <v>711</v>
       </c>
       <c r="D190" s="2">
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>12924</v>
+        <v>14925</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C191" s="4">
-        <v>20</v>
+        <v>1190</v>
       </c>
       <c r="D191" s="2">
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>14753</v>
+        <v>15176</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>178</v>
       </c>
       <c r="C192" s="4">
-        <v>711</v>
+        <v>150</v>
       </c>
       <c r="D192" s="2">
         <v>9</v>
       </c>
       <c r="E192" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>14925</v>
+        <v>15178</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C193" s="4">
-        <v>1360</v>
+        <v>150</v>
       </c>
       <c r="D193" s="2">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>15176</v>
+        <v>15180</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C194" s="4">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D194" s="2">
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>15178</v>
+        <v>15181</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C195" s="4">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="D195" s="2">
         <v>9</v>
       </c>
       <c r="E195" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>15180</v>
+        <v>15182</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C196" s="4">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D196" s="2">
         <v>9</v>
       </c>
       <c r="E196" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>15181</v>
+        <v>15183</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C197" s="4">
-        <v>210</v>
+        <v>1540</v>
       </c>
       <c r="D197" s="2">
         <v>9</v>
       </c>
       <c r="E197" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>15182</v>
+        <v>15184</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C198" s="4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D198" s="2">
         <v>9</v>
       </c>
       <c r="E198" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>15183</v>
+        <v>15185</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C199" s="4">
-        <v>1540</v>
+        <v>50</v>
       </c>
       <c r="D199" s="2">
         <v>9</v>
       </c>
       <c r="E199" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>15184</v>
+        <v>15187</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C200" s="4">
-        <v>200</v>
+        <v>41.5</v>
       </c>
       <c r="D200" s="2">
         <v>9</v>
       </c>
       <c r="E200" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>15185</v>
+        <v>15187</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C201" s="4">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="D201" s="2">
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>15187</v>
+        <v>16336</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C202" s="4">
-        <v>41.5</v>
+        <v>180</v>
       </c>
       <c r="D202" s="2">
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
-        <v>15187</v>
+        <v>16336</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C203" s="4">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D203" s="2">
         <v>9</v>
       </c>
       <c r="E203" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -4526,54 +4523,37 @@
         <v>16336</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C204" s="4">
-        <v>180</v>
+        <v>3060</v>
       </c>
       <c r="D204" s="2">
         <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
-        <v>16336</v>
+        <v>16684</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C205" s="4">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="D205" s="2">
         <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C206" s="4">
-        <v>720</v>
-      </c>
-      <c r="D206" s="2">
-        <v>9</v>
-      </c>
-      <c r="E206" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E203" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>

--- a/data-source/ESTOQUEQUIMICOS.xlsx
+++ b/data-source/ESTOQUEQUIMICOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{456BA992-3F33-4626-9BFC-A94C96A28811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ED85D5C-6219-4A4F-A2A9-F47407B1B4FB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD17542-BBA7-45E6-A128-B4D037E0B204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="203">
   <si>
     <t>Produto</t>
   </si>
@@ -219,9 +219,6 @@
     <t>SOLVENTE MEK</t>
   </si>
   <si>
-    <t>SOLVENTE ALCOOL ETILICO</t>
-  </si>
-  <si>
     <t>SOLVENTE THINNER</t>
   </si>
   <si>
@@ -246,9 +243,6 @@
     <t>RESINA RUBRAS 2910</t>
   </si>
   <si>
-    <t>RESINA STAHL 4715</t>
-  </si>
-  <si>
     <t>RESINA STAHL 4769</t>
   </si>
   <si>
@@ -285,9 +279,6 @@
     <t>ADITIVO SILICONE NIV -  ROMANA</t>
   </si>
   <si>
-    <t>BC 100 SILVER WHITE 10 - BRASCHEMICAL</t>
-  </si>
-  <si>
     <t>RESINA CORIUM CFNLAQ 21601N</t>
   </si>
   <si>
@@ -649,6 +640,12 @@
   </si>
   <si>
     <t>RESINA LR206M-3 (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>PIGMENTO PEROLADO AG/KW 502 RED BROWN</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1054,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1081,7 +1078,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1094,11 +1091,11 @@
       <c r="C2" s="4">
         <v>384</v>
       </c>
-      <c r="D2" s="2">
-        <v>9</v>
+      <c r="D2" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1106,16 +1103,16 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C3" s="4">
         <v>205</v>
       </c>
-      <c r="D3" s="2">
-        <v>9</v>
+      <c r="D3" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1128,8 +1125,8 @@
       <c r="C4" s="4">
         <v>172.5</v>
       </c>
-      <c r="D4" s="2">
-        <v>9</v>
+      <c r="D4" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1143,13 +1140,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>150</v>
-      </c>
-      <c r="D5" s="2">
-        <v>9</v>
+        <v>140</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1162,11 +1159,11 @@
       <c r="C6" s="4">
         <v>40</v>
       </c>
-      <c r="D6" s="2">
-        <v>9</v>
+      <c r="D6" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1174,16 +1171,16 @@
         <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C7" s="4">
         <v>40</v>
       </c>
-      <c r="D7" s="2">
-        <v>9</v>
+      <c r="D7" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1196,11 +1193,11 @@
       <c r="C8" s="4">
         <v>13.3</v>
       </c>
-      <c r="D8" s="2">
-        <v>9</v>
+      <c r="D8" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1213,11 +1210,11 @@
       <c r="C9" s="4">
         <v>180</v>
       </c>
-      <c r="D9" s="2">
-        <v>9</v>
+      <c r="D9" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1230,11 +1227,11 @@
       <c r="C10" s="4">
         <v>470</v>
       </c>
-      <c r="D10" s="2">
-        <v>9</v>
+      <c r="D10" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1247,11 +1244,11 @@
       <c r="C11" s="4">
         <v>410</v>
       </c>
-      <c r="D11" s="2">
-        <v>9</v>
+      <c r="D11" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1262,10 +1259,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>4337</v>
-      </c>
-      <c r="D12" s="2">
-        <v>9</v>
+        <v>3472</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -1279,10 +1276,10 @@
         <v>14</v>
       </c>
       <c r="C13" s="4">
-        <v>186</v>
-      </c>
-      <c r="D13" s="2">
-        <v>9</v>
+        <v>372</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -1298,11 +1295,11 @@
       <c r="C14" s="4">
         <v>25</v>
       </c>
-      <c r="D14" s="2">
-        <v>9</v>
+      <c r="D14" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E14" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1313,13 +1310,13 @@
         <v>16</v>
       </c>
       <c r="C15" s="4">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2">
-        <v>9</v>
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1332,11 +1329,11 @@
       <c r="C16" s="4">
         <v>1.4</v>
       </c>
-      <c r="D16" s="2">
-        <v>9</v>
+      <c r="D16" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1349,11 +1346,11 @@
       <c r="C17" s="4">
         <v>0.89</v>
       </c>
-      <c r="D17" s="2">
-        <v>9</v>
+      <c r="D17" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1366,11 +1363,11 @@
       <c r="C18" s="4">
         <v>101.7</v>
       </c>
-      <c r="D18" s="2">
-        <v>9</v>
+      <c r="D18" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1383,11 +1380,11 @@
       <c r="C19" s="4">
         <v>95</v>
       </c>
-      <c r="D19" s="2">
-        <v>9</v>
+      <c r="D19" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1400,11 +1397,11 @@
       <c r="C20" s="4">
         <v>2.85</v>
       </c>
-      <c r="D20" s="2">
-        <v>9</v>
+      <c r="D20" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1417,11 +1414,11 @@
       <c r="C21" s="4">
         <v>0.65</v>
       </c>
-      <c r="D21" s="2">
-        <v>9</v>
+      <c r="D21" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1434,11 +1431,11 @@
       <c r="C22" s="4">
         <v>2.6</v>
       </c>
-      <c r="D22" s="2">
-        <v>9</v>
+      <c r="D22" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1451,11 +1448,11 @@
       <c r="C23" s="4">
         <v>7.6</v>
       </c>
-      <c r="D23" s="2">
-        <v>9</v>
+      <c r="D23" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E23" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1468,11 +1465,11 @@
       <c r="C24" s="4">
         <v>4.8899999999999997</v>
       </c>
-      <c r="D24" s="2">
-        <v>9</v>
+      <c r="D24" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E24" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1485,11 +1482,11 @@
       <c r="C25" s="4">
         <v>5</v>
       </c>
-      <c r="D25" s="2">
-        <v>9</v>
+      <c r="D25" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E25" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1502,11 +1499,11 @@
       <c r="C26" s="4">
         <v>5</v>
       </c>
-      <c r="D26" s="2">
-        <v>9</v>
+      <c r="D26" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1519,11 +1516,11 @@
       <c r="C27" s="4">
         <v>5</v>
       </c>
-      <c r="D27" s="2">
-        <v>9</v>
+      <c r="D27" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1536,11 +1533,11 @@
       <c r="C28" s="4">
         <v>5</v>
       </c>
-      <c r="D28" s="2">
-        <v>9</v>
+      <c r="D28" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E28" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1553,11 +1550,11 @@
       <c r="C29" s="4">
         <v>5</v>
       </c>
-      <c r="D29" s="2">
-        <v>9</v>
+      <c r="D29" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1570,11 +1567,11 @@
       <c r="C30" s="4">
         <v>10</v>
       </c>
-      <c r="D30" s="2">
-        <v>9</v>
+      <c r="D30" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1587,11 +1584,11 @@
       <c r="C31" s="4">
         <v>4.96</v>
       </c>
-      <c r="D31" s="2">
-        <v>9</v>
+      <c r="D31" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E31" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1604,11 +1601,11 @@
       <c r="C32" s="4">
         <v>9</v>
       </c>
-      <c r="D32" s="2">
-        <v>9</v>
+      <c r="D32" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1621,11 +1618,11 @@
       <c r="C33" s="4">
         <v>106.64</v>
       </c>
-      <c r="D33" s="2">
-        <v>9</v>
+      <c r="D33" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1638,11 +1635,11 @@
       <c r="C34" s="4">
         <v>183.9</v>
       </c>
-      <c r="D34" s="2">
-        <v>9</v>
+      <c r="D34" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1653,13 +1650,13 @@
         <v>36</v>
       </c>
       <c r="C35" s="4">
-        <v>480</v>
-      </c>
-      <c r="D35" s="2">
-        <v>9</v>
+        <v>375</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E35" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1672,11 +1669,11 @@
       <c r="C36" s="4">
         <v>44</v>
       </c>
-      <c r="D36" s="2">
-        <v>9</v>
+      <c r="D36" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E36" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1689,11 +1686,11 @@
       <c r="C37" s="4">
         <v>2.23</v>
       </c>
-      <c r="D37" s="2">
-        <v>9</v>
+      <c r="D37" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E37" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1706,11 +1703,11 @@
       <c r="C38" s="4">
         <v>3</v>
       </c>
-      <c r="D38" s="2">
-        <v>9</v>
+      <c r="D38" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E38" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1723,11 +1720,11 @@
       <c r="C39" s="4">
         <v>5.9</v>
       </c>
-      <c r="D39" s="2">
-        <v>9</v>
+      <c r="D39" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1740,11 +1737,11 @@
       <c r="C40" s="4">
         <v>19.5</v>
       </c>
-      <c r="D40" s="2">
-        <v>9</v>
+      <c r="D40" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E40" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1757,11 +1754,11 @@
       <c r="C41" s="4">
         <v>12.1</v>
       </c>
-      <c r="D41" s="2">
-        <v>9</v>
+      <c r="D41" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1774,11 +1771,11 @@
       <c r="C42" s="4">
         <v>13</v>
       </c>
-      <c r="D42" s="2">
-        <v>9</v>
+      <c r="D42" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1791,11 +1788,11 @@
       <c r="C43" s="4">
         <v>80</v>
       </c>
-      <c r="D43" s="2">
-        <v>9</v>
+      <c r="D43" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1808,11 +1805,11 @@
       <c r="C44" s="4">
         <v>175</v>
       </c>
-      <c r="D44" s="2">
-        <v>9</v>
+      <c r="D44" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1823,13 +1820,13 @@
         <v>46</v>
       </c>
       <c r="C45" s="4">
-        <v>200</v>
-      </c>
-      <c r="D45" s="2">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E45" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1842,11 +1839,11 @@
       <c r="C46" s="4">
         <v>40</v>
       </c>
-      <c r="D46" s="2">
-        <v>9</v>
+      <c r="D46" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E46" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1859,11 +1856,11 @@
       <c r="C47" s="4">
         <v>100</v>
       </c>
-      <c r="D47" s="2">
-        <v>9</v>
+      <c r="D47" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E47" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1876,11 +1873,11 @@
       <c r="C48" s="4">
         <v>50</v>
       </c>
-      <c r="D48" s="2">
-        <v>9</v>
+      <c r="D48" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E48" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1893,11 +1890,11 @@
       <c r="C49" s="4">
         <v>40</v>
       </c>
-      <c r="D49" s="2">
-        <v>9</v>
+      <c r="D49" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E49" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1910,11 +1907,11 @@
       <c r="C50" s="4">
         <v>18</v>
       </c>
-      <c r="D50" s="2">
-        <v>9</v>
+      <c r="D50" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E50" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1927,11 +1924,11 @@
       <c r="C51" s="4">
         <v>8</v>
       </c>
-      <c r="D51" s="2">
-        <v>9</v>
+      <c r="D51" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E51" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1944,11 +1941,11 @@
       <c r="C52" s="4">
         <v>13.8</v>
       </c>
-      <c r="D52" s="2">
-        <v>9</v>
+      <c r="D52" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E52" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1959,13 +1956,13 @@
         <v>54</v>
       </c>
       <c r="C53" s="4">
-        <v>769</v>
-      </c>
-      <c r="D53" s="2">
-        <v>9</v>
+        <v>599</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E53" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1978,11 +1975,11 @@
       <c r="C54" s="4">
         <v>25</v>
       </c>
-      <c r="D54" s="2">
-        <v>9</v>
+      <c r="D54" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E54" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1995,11 +1992,11 @@
       <c r="C55" s="4">
         <v>127.8</v>
       </c>
-      <c r="D55" s="2">
-        <v>9</v>
+      <c r="D55" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E55" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2012,11 +2009,11 @@
       <c r="C56" s="4">
         <v>17.899999999999999</v>
       </c>
-      <c r="D56" s="2">
-        <v>9</v>
+      <c r="D56" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E56" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2027,10 +2024,10 @@
         <v>58</v>
       </c>
       <c r="C57" s="4">
-        <v>1140</v>
-      </c>
-      <c r="D57" s="2">
-        <v>9</v>
+        <v>760</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E57" t="s">
         <v>6</v>
@@ -2041,13 +2038,13 @@
         <v>135</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C58" s="4">
         <v>320</v>
       </c>
-      <c r="D58" s="2">
-        <v>9</v>
+      <c r="D58" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E58" t="s">
         <v>6</v>
@@ -2063,8 +2060,8 @@
       <c r="C59" s="4">
         <v>657.5</v>
       </c>
-      <c r="D59" s="2">
-        <v>9</v>
+      <c r="D59" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E59" t="s">
         <v>6</v>
@@ -2072,16 +2069,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C60" s="4">
-        <v>22</v>
-      </c>
-      <c r="D60" s="2">
-        <v>9</v>
+        <v>577</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E60" t="s">
         <v>6</v>
@@ -2089,636 +2086,636 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C61" s="4">
-        <v>577</v>
-      </c>
-      <c r="D61" s="2">
-        <v>9</v>
+        <v>2160</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C62" s="4">
-        <v>2160</v>
-      </c>
-      <c r="D62" s="2">
-        <v>9</v>
+        <v>100.04900000000001</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E62" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C63" s="4">
-        <v>100.04900000000001</v>
-      </c>
-      <c r="D63" s="2">
-        <v>9</v>
+        <v>15.55</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E63" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C64" s="4">
-        <v>15.55</v>
-      </c>
-      <c r="D64" s="2">
-        <v>9</v>
+        <v>21.7</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E64" t="s">
-        <v>189</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="4">
-        <v>21.7</v>
-      </c>
-      <c r="D65" s="2">
-        <v>9</v>
+        <v>2.5</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C66" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="D66" s="2">
-        <v>9</v>
+        <v>0.7</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E66" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C67" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="D67" s="2">
-        <v>9</v>
+        <v>60.8</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E67" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C68" s="4">
-        <v>60.8</v>
-      </c>
-      <c r="D68" s="2">
-        <v>9</v>
+        <v>185</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E68" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="4">
-        <v>740</v>
-      </c>
-      <c r="D69" s="2">
-        <v>9</v>
+        <v>190</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E69" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="4">
-        <v>185</v>
-      </c>
-      <c r="D70" s="2">
-        <v>9</v>
+        <v>31.83</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E70" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C71" s="4">
-        <v>190</v>
-      </c>
-      <c r="D71" s="2">
-        <v>9</v>
+        <v>151.4</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E71" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C72" s="4">
-        <v>31.83</v>
-      </c>
-      <c r="D72" s="2">
-        <v>9</v>
+        <v>36</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E72" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C73" s="4">
-        <v>151.4</v>
-      </c>
-      <c r="D73" s="2">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E73" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C74" s="4">
-        <v>36</v>
-      </c>
-      <c r="D74" s="2">
-        <v>9</v>
+        <v>54</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E74" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C75" s="4">
-        <v>11</v>
-      </c>
-      <c r="D75" s="2">
-        <v>9</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E75" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C76" s="4">
-        <v>54</v>
-      </c>
-      <c r="D76" s="2">
-        <v>9</v>
+        <v>19.559999999999999</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E76" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C77" s="4">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="D77" s="2">
-        <v>9</v>
+        <v>9.65</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E77" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C78" s="4">
-        <v>19.559999999999999</v>
-      </c>
-      <c r="D78" s="2">
-        <v>9</v>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E78" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>174</v>
+        <v>404</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C79" s="4">
-        <v>9.65</v>
-      </c>
-      <c r="D79" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E79" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>186</v>
+        <v>870</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C80" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D80" s="2">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E80" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>404</v>
+        <v>936</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C81" s="4">
-        <v>25</v>
-      </c>
-      <c r="D81" s="2">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E81" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>785</v>
+        <v>1494</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C82" s="4">
-        <v>25</v>
-      </c>
-      <c r="D82" s="2">
-        <v>9</v>
+        <v>329.4</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E82" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>870</v>
+        <v>1610</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C83" s="4">
-        <v>13</v>
-      </c>
-      <c r="D83" s="2">
-        <v>9</v>
+        <v>90.6</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E83" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>936</v>
+        <v>1961</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C84" s="4">
-        <v>5</v>
-      </c>
-      <c r="D84" s="2">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E84" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>1494</v>
+        <v>2215</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C85" s="4">
-        <v>329.4</v>
-      </c>
-      <c r="D85" s="2">
-        <v>9</v>
+        <v>24.658000000000001</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E85" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>1610</v>
+        <v>2223</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C86" s="4">
-        <v>90.6</v>
-      </c>
-      <c r="D86" s="2">
-        <v>9</v>
+        <v>211</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E86" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>1961</v>
+        <v>2572</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C87" s="4">
-        <v>17</v>
-      </c>
-      <c r="D87" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E87" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>2215</v>
+        <v>2728</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C88" s="4">
-        <v>24.658000000000001</v>
-      </c>
-      <c r="D88" s="2">
-        <v>9</v>
+        <v>131.4</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E88" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>2223</v>
+        <v>2794</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C89" s="4">
-        <v>211</v>
-      </c>
-      <c r="D89" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E89" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>2572</v>
+        <v>2833</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C90" s="4">
-        <v>25</v>
-      </c>
-      <c r="D90" s="2">
-        <v>9</v>
+        <v>30.7</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E90" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>2728</v>
+        <v>3202</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C91" s="4">
-        <v>131.4</v>
-      </c>
-      <c r="D91" s="2">
-        <v>9</v>
+        <v>7.9</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E91" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>2794</v>
+        <v>3203</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C92" s="4">
-        <v>100</v>
-      </c>
-      <c r="D92" s="2">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E92" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>2833</v>
+        <v>3204</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C93" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="D93" s="2">
-        <v>9</v>
+        <v>301</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E93" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>3202</v>
+        <v>3220</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C94" s="4">
-        <v>7.9</v>
-      </c>
-      <c r="D94" s="2">
-        <v>9</v>
+        <v>21</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E94" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>3203</v>
+        <v>3643</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C95" s="4">
-        <v>28</v>
-      </c>
-      <c r="D95" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>3204</v>
+        <v>3932</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C96" s="4">
-        <v>301</v>
-      </c>
-      <c r="D96" s="2">
-        <v>9</v>
+        <v>35</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E96" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>3220</v>
+        <v>3933</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C97" s="4">
-        <v>21</v>
-      </c>
-      <c r="D97" s="2">
-        <v>9</v>
+        <v>55</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E97" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>3643</v>
+        <v>3935</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>98</v>
@@ -2726,8 +2723,8 @@
       <c r="C98" s="4">
         <v>25</v>
       </c>
-      <c r="D98" s="2">
-        <v>9</v>
+      <c r="D98" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E98" t="s">
         <v>194</v>
@@ -2735,594 +2732,594 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>3932</v>
+        <v>3936</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C99" s="4">
-        <v>35</v>
-      </c>
-      <c r="D99" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E99" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>3933</v>
+        <v>3937</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C100" s="4">
-        <v>55</v>
-      </c>
-      <c r="D100" s="2">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E100" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>3935</v>
+        <v>3962</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C101" s="4">
-        <v>25</v>
-      </c>
-      <c r="D101" s="2">
-        <v>9</v>
+        <v>135.82300000000001</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E101" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>3936</v>
+        <v>4045</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C102" s="4">
-        <v>25</v>
-      </c>
-      <c r="D102" s="2">
-        <v>9</v>
+        <v>13.3</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E102" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>3937</v>
+        <v>4047</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C103" s="4">
-        <v>20</v>
-      </c>
-      <c r="D103" s="2">
-        <v>9</v>
+        <v>20.887</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E103" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>3962</v>
+        <v>4106</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C104" s="4">
-        <v>135.82300000000001</v>
-      </c>
-      <c r="D104" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E104" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>4045</v>
+        <v>4161</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>105</v>
       </c>
       <c r="C105" s="4">
-        <v>13.3</v>
-      </c>
-      <c r="D105" s="2">
-        <v>9</v>
+        <v>94</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E105" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>4047</v>
+        <v>4256</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C106" s="4">
-        <v>20.887</v>
-      </c>
-      <c r="D106" s="2">
-        <v>9</v>
+        <v>40</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E106" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>4106</v>
+        <v>4319</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>107</v>
       </c>
       <c r="C107" s="4">
-        <v>50</v>
-      </c>
-      <c r="D107" s="2">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E107" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>4161</v>
+        <v>4329</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C108" s="4">
-        <v>94</v>
-      </c>
-      <c r="D108" s="2">
-        <v>9</v>
+        <v>40</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E108" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>4256</v>
+        <v>4377</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C109" s="4">
-        <v>40</v>
-      </c>
-      <c r="D109" s="2">
-        <v>9</v>
+        <v>29.5</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E109" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>4319</v>
+        <v>4477</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C110" s="4">
-        <v>30</v>
-      </c>
-      <c r="D110" s="2">
-        <v>9</v>
+        <v>18.8</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E110" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>4329</v>
+        <v>4478</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C111" s="4">
-        <v>40</v>
-      </c>
-      <c r="D111" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E111" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>4377</v>
+        <v>4478</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C112" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="D112" s="2">
-        <v>9</v>
+        <v>800</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E112" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>4477</v>
+        <v>4478</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C113" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="D113" s="2">
-        <v>9</v>
+        <v>2100</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E113" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C114" s="4">
-        <v>100</v>
-      </c>
-      <c r="D114" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E114" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>4478</v>
+        <v>4729</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C115" s="4">
-        <v>2100</v>
-      </c>
-      <c r="D115" s="2">
-        <v>9</v>
+        <v>318.8</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E115" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>4479</v>
+        <v>4730</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C116" s="4">
-        <v>150</v>
-      </c>
-      <c r="D116" s="2">
-        <v>9</v>
+        <v>144</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E116" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>4729</v>
+        <v>4799</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C117" s="4">
-        <v>318.8</v>
-      </c>
-      <c r="D117" s="2">
-        <v>9</v>
+        <v>218.01</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E117" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>4730</v>
+        <v>4848</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C118" s="4">
-        <v>144</v>
-      </c>
-      <c r="D118" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E118" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>4799</v>
+        <v>5022</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C119" s="4">
-        <v>218.01</v>
-      </c>
-      <c r="D119" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E119" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>4848</v>
+        <v>5087</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="C120" s="4">
-        <v>25</v>
-      </c>
-      <c r="D120" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E120" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>5022</v>
+        <v>5117</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C121" s="4">
-        <v>25</v>
-      </c>
-      <c r="D121" s="2">
-        <v>9</v>
+        <v>38</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E121" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>5087</v>
+        <v>5120</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C122" s="4">
         <v>25</v>
       </c>
-      <c r="D122" s="2">
-        <v>9</v>
+      <c r="D122" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E122" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>5117</v>
+        <v>5187</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C123" s="4">
-        <v>38</v>
-      </c>
-      <c r="D123" s="2">
-        <v>9</v>
+        <v>190</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E123" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>5187</v>
+        <v>5260</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C124" s="4">
-        <v>190</v>
-      </c>
-      <c r="D124" s="2">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E124" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>5260</v>
+        <v>5373</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C125" s="4">
-        <v>5</v>
-      </c>
-      <c r="D125" s="2">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E125" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>5373</v>
+        <v>5736</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C126" s="4">
-        <v>20</v>
-      </c>
-      <c r="D126" s="2">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E126" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>5736</v>
+        <v>5741</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C127" s="4">
         <v>5</v>
       </c>
-      <c r="D127" s="2">
-        <v>9</v>
+      <c r="D127" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E127" t="s">
-        <v>189</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C128" s="4">
-        <v>5</v>
-      </c>
-      <c r="D128" s="2">
-        <v>9</v>
+        <v>19.2</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E128" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C129" s="4">
-        <v>19.2</v>
-      </c>
-      <c r="D129" s="2">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E129" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>5743</v>
+        <v>5747</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C130" s="4">
-        <v>2</v>
-      </c>
-      <c r="D130" s="2">
-        <v>9</v>
+        <v>5.98</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E130" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C131" s="4">
-        <v>5.98</v>
-      </c>
-      <c r="D131" s="2">
-        <v>9</v>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>5748</v>
+        <v>5750</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C132" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D132" s="2">
-        <v>9</v>
+        <v>28.7</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E132" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>5750</v>
+        <v>5796</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C133" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="D133" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E133" t="s">
         <v>193</v>
@@ -3333,33 +3330,33 @@
         <v>5796</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C134" s="4">
-        <v>50</v>
-      </c>
-      <c r="D134" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E134" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C135" s="4">
-        <v>150</v>
-      </c>
-      <c r="D135" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E135" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3367,98 +3364,98 @@
         <v>5797</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C136" s="4">
-        <v>100</v>
-      </c>
-      <c r="D136" s="2">
-        <v>9</v>
+        <v>400</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E136" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>5809</v>
+        <v>5797</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C137" s="4">
-        <v>359.4</v>
-      </c>
-      <c r="D137" s="2">
-        <v>9</v>
+        <v>800</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E137" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C138" s="4">
-        <v>1260</v>
-      </c>
-      <c r="D138" s="2">
-        <v>9</v>
+        <v>359.4</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E138" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>5811</v>
+        <v>5810</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C139" s="4">
-        <v>160.30000000000001</v>
-      </c>
-      <c r="D139" s="2">
-        <v>9</v>
+        <v>1260</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E139" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C140" s="4">
-        <v>159.80000000000001</v>
-      </c>
-      <c r="D140" s="2">
-        <v>9</v>
+        <v>160.30000000000001</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E140" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>5856</v>
+        <v>5812</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C141" s="4">
-        <v>110</v>
-      </c>
-      <c r="D141" s="2">
-        <v>9</v>
+        <v>159.80000000000001</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E141" t="s">
         <v>189</v>
@@ -3466,19 +3463,19 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>6505</v>
+        <v>5856</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C142" s="4">
-        <v>50</v>
-      </c>
-      <c r="D142" s="2">
-        <v>9</v>
+        <v>110</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E142" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -3486,33 +3483,33 @@
         <v>6505</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C143" s="4">
-        <v>100</v>
-      </c>
-      <c r="D143" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E143" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>6506</v>
+        <v>6505</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C144" s="4">
-        <v>150</v>
-      </c>
-      <c r="D144" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E144" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -3520,676 +3517,676 @@
         <v>6506</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C145" s="4">
-        <v>450</v>
-      </c>
-      <c r="D145" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E145" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>6507</v>
+        <v>6506</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C146" s="4">
-        <v>100</v>
-      </c>
-      <c r="D146" s="2">
-        <v>9</v>
+        <v>450</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E146" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>6507</v>
+        <v>6506</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C147" s="4">
-        <v>400</v>
-      </c>
-      <c r="D147" s="2">
-        <v>9</v>
+        <v>800</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E147" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>6508</v>
+        <v>6507</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C148" s="4">
-        <v>14.9</v>
-      </c>
-      <c r="D148" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E148" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>6508</v>
+        <v>6507</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C149" s="4">
-        <v>150</v>
-      </c>
-      <c r="D149" s="2">
-        <v>9</v>
+        <v>400</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E149" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>6509</v>
+        <v>6508</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C150" s="4">
-        <v>82.8</v>
-      </c>
-      <c r="D150" s="2">
-        <v>9</v>
+        <v>14.9</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E150" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>6510</v>
+        <v>6508</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C151" s="4">
-        <v>50</v>
-      </c>
-      <c r="D151" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E151" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>6510</v>
+        <v>6509</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C152" s="4">
-        <v>100</v>
-      </c>
-      <c r="D152" s="2">
-        <v>9</v>
+        <v>82.8</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E152" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>6511</v>
+        <v>6510</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C153" s="4">
-        <v>300</v>
-      </c>
-      <c r="D153" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E153" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>6512</v>
+        <v>6510</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C154" s="4">
-        <v>24.998999999999999</v>
-      </c>
-      <c r="D154" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E154" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>6514</v>
+        <v>6511</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C155" s="4">
-        <v>100</v>
-      </c>
-      <c r="D155" s="2">
-        <v>9</v>
+        <v>300</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E155" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>6828</v>
+        <v>6512</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C156" s="4">
-        <v>150</v>
-      </c>
-      <c r="D156" s="2">
-        <v>9</v>
+        <v>24.998999999999999</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E156" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>8329</v>
+        <v>6514</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C157" s="4">
-        <v>3800</v>
-      </c>
-      <c r="D157" s="2">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E157" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>8894</v>
+        <v>6514</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C158" s="4">
-        <v>540</v>
-      </c>
-      <c r="D158" s="2">
-        <v>9</v>
+        <v>250</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E158" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>8895</v>
+        <v>6828</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C159" s="4">
-        <v>36.6</v>
-      </c>
-      <c r="D159" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E159" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>8930</v>
+        <v>8329</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C160" s="4">
-        <v>25</v>
-      </c>
-      <c r="D160" s="2">
-        <v>9</v>
+        <v>2850</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E160" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>9716</v>
+        <v>8894</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C161" s="4">
-        <v>18</v>
-      </c>
-      <c r="D161" s="2">
-        <v>9</v>
+        <v>540</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E161" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>9716</v>
+        <v>8895</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C162" s="4">
-        <v>18</v>
-      </c>
-      <c r="D162" s="2">
-        <v>9</v>
+        <v>36.6</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E162" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>10497</v>
+        <v>8930</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C163" s="4">
-        <v>2470</v>
-      </c>
-      <c r="D163" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E163" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>10907</v>
+        <v>9716</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C164" s="4">
-        <v>2</v>
-      </c>
-      <c r="D164" s="2">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E164" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>11259</v>
+        <v>9716</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C165" s="4">
-        <v>25</v>
-      </c>
-      <c r="D165" s="2">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E165" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>11370</v>
+        <v>10497</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C166" s="4">
-        <v>180</v>
-      </c>
-      <c r="D166" s="2">
-        <v>9</v>
+        <v>1900</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E166" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>11370</v>
+        <v>10907</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C167" s="4">
-        <v>2700</v>
-      </c>
-      <c r="D167" s="2">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E167" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>11370</v>
+        <v>11259</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C168" s="4">
-        <v>3960</v>
-      </c>
-      <c r="D168" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E168" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>11371</v>
+        <v>11370</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C169" s="4">
-        <v>897</v>
-      </c>
-      <c r="D169" s="2">
-        <v>9</v>
+        <v>180</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E169" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>11372</v>
+        <v>11370</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C170" s="4">
-        <v>540</v>
-      </c>
-      <c r="D170" s="2">
-        <v>9</v>
+        <v>2700</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E170" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>11373</v>
+        <v>11370</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C171" s="4">
-        <v>705</v>
-      </c>
-      <c r="D171" s="2">
-        <v>9</v>
+        <v>3060</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E171" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>11374</v>
+        <v>11371</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="C172" s="4">
-        <v>2160</v>
-      </c>
-      <c r="D172" s="2">
-        <v>9</v>
+        <v>897</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E172" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>11377</v>
+        <v>11372</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C173" s="4">
-        <v>300</v>
-      </c>
-      <c r="D173" s="2">
-        <v>9</v>
+        <v>540</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E173" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>11377</v>
+        <v>11373</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C174" s="4">
-        <v>2700</v>
-      </c>
-      <c r="D174" s="2">
-        <v>9</v>
+        <v>705</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E174" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>11378</v>
+        <v>11374</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="C175" s="4">
-        <v>360</v>
-      </c>
-      <c r="D175" s="2">
-        <v>9</v>
+        <v>1980</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E175" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>11379</v>
+        <v>11377</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C176" s="4">
-        <v>180</v>
-      </c>
-      <c r="D176" s="2">
-        <v>9</v>
+        <v>300</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E176" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>11380</v>
+        <v>11377</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C177" s="4">
-        <v>180</v>
-      </c>
-      <c r="D177" s="2">
-        <v>9</v>
+        <v>2700</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E177" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>11612</v>
+        <v>11378</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C178" s="4">
-        <v>25</v>
-      </c>
-      <c r="D178" s="2">
-        <v>9</v>
+        <v>360</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E178" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>11849</v>
+        <v>11379</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C179" s="4">
-        <v>50</v>
-      </c>
-      <c r="D179" s="2">
-        <v>9</v>
+        <v>180</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E179" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>12710</v>
+        <v>11379</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C180" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="D180" s="2">
-        <v>9</v>
+        <v>1440</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E180" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>12711</v>
+        <v>11380</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C181" s="4">
-        <v>1</v>
-      </c>
-      <c r="D181" s="2">
-        <v>9</v>
+        <v>180</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E181" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>12712</v>
+        <v>11612</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C182" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="D182" s="2">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E182" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>12713</v>
+        <v>11849</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C183" s="4">
-        <v>1</v>
-      </c>
-      <c r="D183" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E183" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>12714</v>
+        <v>12710</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C184" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D184" s="2">
-        <v>9</v>
+        <v>2.5</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E184" t="s">
         <v>189</v>
@@ -4197,84 +4194,84 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>12715</v>
+        <v>12711</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C185" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D185" s="2">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E185" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>12716</v>
+        <v>12712</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C186" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D186" s="2">
-        <v>9</v>
+        <v>0.06</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E186" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>12717</v>
+        <v>12713</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C187" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D187" s="2">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E187" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>12718</v>
+        <v>12714</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C188" s="4">
-        <v>1</v>
-      </c>
-      <c r="D188" s="2">
-        <v>9</v>
+        <v>0.05</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E188" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>12924</v>
+        <v>12715</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C189" s="4">
-        <v>20</v>
-      </c>
-      <c r="D189" s="2">
-        <v>9</v>
+        <v>0.05</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E189" t="s">
         <v>189</v>
@@ -4282,16 +4279,16 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>14753</v>
+        <v>12716</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C190" s="4">
-        <v>711</v>
-      </c>
-      <c r="D190" s="2">
-        <v>9</v>
+        <v>0.05</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E190" t="s">
         <v>189</v>
@@ -4299,16 +4296,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>14925</v>
+        <v>12717</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="C191" s="4">
-        <v>1190</v>
-      </c>
-      <c r="D191" s="2">
-        <v>9</v>
+        <v>0.05</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E191" t="s">
         <v>189</v>
@@ -4316,240 +4313,308 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>15176</v>
+        <v>12718</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C192" s="4">
-        <v>150</v>
-      </c>
-      <c r="D192" s="2">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E192" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>15178</v>
+        <v>12924</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C193" s="4">
-        <v>150</v>
-      </c>
-      <c r="D193" s="2">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E193" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>15180</v>
+        <v>14753</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C194" s="4">
-        <v>250</v>
-      </c>
-      <c r="D194" s="2">
-        <v>9</v>
+        <v>711</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E194" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>15181</v>
+        <v>14925</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C195" s="4">
-        <v>210</v>
-      </c>
-      <c r="D195" s="2">
-        <v>9</v>
+        <v>1020</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E195" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>15182</v>
+        <v>15176</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C196" s="4">
-        <v>210</v>
-      </c>
-      <c r="D196" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E196" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>15183</v>
+        <v>15178</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C197" s="4">
-        <v>1540</v>
-      </c>
-      <c r="D197" s="2">
-        <v>9</v>
+        <v>150</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E197" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>15184</v>
+        <v>15180</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C198" s="4">
-        <v>200</v>
-      </c>
-      <c r="D198" s="2">
-        <v>9</v>
+        <v>250</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E198" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>15185</v>
+        <v>15181</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C199" s="4">
-        <v>50</v>
-      </c>
-      <c r="D199" s="2">
-        <v>9</v>
+        <v>210</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E199" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>15187</v>
+        <v>15182</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C200" s="4">
-        <v>41.5</v>
-      </c>
-      <c r="D200" s="2">
-        <v>9</v>
+        <v>210</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E200" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>15187</v>
+        <v>15183</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C201" s="4">
-        <v>125</v>
-      </c>
-      <c r="D201" s="2">
-        <v>9</v>
+        <v>1540</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E201" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>16336</v>
+        <v>15184</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C202" s="4">
-        <v>180</v>
-      </c>
-      <c r="D202" s="2">
-        <v>9</v>
+        <v>200</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E202" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
-        <v>16336</v>
+        <v>15185</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C203" s="4">
-        <v>180</v>
-      </c>
-      <c r="D203" s="2">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E203" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
-        <v>16336</v>
+        <v>15187</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C204" s="4">
-        <v>3060</v>
-      </c>
-      <c r="D204" s="2">
-        <v>9</v>
+        <v>41.5</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E204" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
+        <v>15187</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C205" s="4">
+        <v>125</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E205" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="2">
+        <v>16336</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C206" s="4">
+        <v>180</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E206" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="2">
+        <v>16336</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C207" s="4">
+        <v>3240</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E207" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="2">
         <v>16684</v>
       </c>
-      <c r="B205" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C205" s="4">
-        <v>720</v>
-      </c>
-      <c r="D205" s="2">
-        <v>9</v>
-      </c>
-      <c r="E205" t="s">
-        <v>192</v>
+      <c r="B208" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C208" s="4">
+        <v>540</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E208" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="2">
+        <v>16684</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C209" s="4">
+        <v>2340</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E209" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/ESTOQUEQUIMICOS.xlsx
+++ b/data-source/ESTOQUEQUIMICOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD17542-BBA7-45E6-A128-B4D037E0B204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51B4CEC-D095-4C4A-B940-5EDEFE5818C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="1092" windowWidth="20736" windowHeight="11148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="205">
   <si>
     <t>Produto</t>
   </si>
@@ -642,10 +642,16 @@
     <t>RESINA LR206M-3 (AMERICA ASIA)</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>PIGMENTO PEROLADO AG/KW 502 RED BROWN</t>
+  </si>
+  <si>
+    <t>SOLVENTE ALCOOL ETILICO</t>
+  </si>
+  <si>
+    <t>RESINA STAHL 4715</t>
+  </si>
+  <si>
+    <t>BC 100 SILVER WHITE 10 - BRASCHEMICAL</t>
   </si>
 </sst>
 </file>
@@ -1091,8 +1097,8 @@
       <c r="C2" s="4">
         <v>384</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>201</v>
+      <c r="D2" s="2">
+        <v>9</v>
       </c>
       <c r="E2" t="s">
         <v>186</v>
@@ -1108,8 +1114,8 @@
       <c r="C3" s="4">
         <v>205</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>201</v>
+      <c r="D3" s="2">
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>186</v>
@@ -1125,8 +1131,8 @@
       <c r="C4" s="4">
         <v>172.5</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>201</v>
+      <c r="D4" s="2">
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1142,8 +1148,8 @@
       <c r="C5" s="4">
         <v>140</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>201</v>
+      <c r="D5" s="2">
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>187</v>
@@ -1157,10 +1163,10 @@
         <v>8</v>
       </c>
       <c r="C6" s="4">
-        <v>40</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>201</v>
+        <v>60</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>194</v>
@@ -1176,8 +1182,8 @@
       <c r="C7" s="4">
         <v>40</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>201</v>
+      <c r="D7" s="2">
+        <v>9</v>
       </c>
       <c r="E7" t="s">
         <v>194</v>
@@ -1193,8 +1199,8 @@
       <c r="C8" s="4">
         <v>13.3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>201</v>
+      <c r="D8" s="2">
+        <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>186</v>
@@ -1210,8 +1216,8 @@
       <c r="C9" s="4">
         <v>180</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>201</v>
+      <c r="D9" s="2">
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>186</v>
@@ -1227,8 +1233,8 @@
       <c r="C10" s="4">
         <v>470</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>201</v>
+      <c r="D10" s="2">
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>186</v>
@@ -1244,8 +1250,8 @@
       <c r="C11" s="4">
         <v>410</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>201</v>
+      <c r="D11" s="2">
+        <v>9</v>
       </c>
       <c r="E11" t="s">
         <v>186</v>
@@ -1259,10 +1265,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>3472</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>201</v>
+        <v>2733.8609999999999</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -1278,8 +1284,8 @@
       <c r="C13" s="4">
         <v>372</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>201</v>
+      <c r="D13" s="2">
+        <v>9</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -1295,8 +1301,8 @@
       <c r="C14" s="4">
         <v>25</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>201</v>
+      <c r="D14" s="2">
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>194</v>
@@ -1312,8 +1318,8 @@
       <c r="C15" s="4">
         <v>36</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>201</v>
+      <c r="D15" s="2">
+        <v>9</v>
       </c>
       <c r="E15" t="s">
         <v>187</v>
@@ -1329,8 +1335,8 @@
       <c r="C16" s="4">
         <v>1.4</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>201</v>
+      <c r="D16" s="2">
+        <v>9</v>
       </c>
       <c r="E16" t="s">
         <v>194</v>
@@ -1346,8 +1352,8 @@
       <c r="C17" s="4">
         <v>0.89</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>201</v>
+      <c r="D17" s="2">
+        <v>9</v>
       </c>
       <c r="E17" t="s">
         <v>187</v>
@@ -1363,8 +1369,8 @@
       <c r="C18" s="4">
         <v>101.7</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>201</v>
+      <c r="D18" s="2">
+        <v>9</v>
       </c>
       <c r="E18" t="s">
         <v>186</v>
@@ -1380,8 +1386,8 @@
       <c r="C19" s="4">
         <v>95</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>201</v>
+      <c r="D19" s="2">
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>186</v>
@@ -1397,8 +1403,8 @@
       <c r="C20" s="4">
         <v>2.85</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>201</v>
+      <c r="D20" s="2">
+        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>194</v>
@@ -1414,8 +1420,8 @@
       <c r="C21" s="4">
         <v>0.65</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>201</v>
+      <c r="D21" s="2">
+        <v>9</v>
       </c>
       <c r="E21" t="s">
         <v>194</v>
@@ -1431,8 +1437,8 @@
       <c r="C22" s="4">
         <v>2.6</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>201</v>
+      <c r="D22" s="2">
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>194</v>
@@ -1448,8 +1454,8 @@
       <c r="C23" s="4">
         <v>7.6</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>201</v>
+      <c r="D23" s="2">
+        <v>9</v>
       </c>
       <c r="E23" t="s">
         <v>187</v>
@@ -1465,8 +1471,8 @@
       <c r="C24" s="4">
         <v>4.8899999999999997</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>201</v>
+      <c r="D24" s="2">
+        <v>9</v>
       </c>
       <c r="E24" t="s">
         <v>188</v>
@@ -1482,8 +1488,8 @@
       <c r="C25" s="4">
         <v>5</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>201</v>
+      <c r="D25" s="2">
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>188</v>
@@ -1499,8 +1505,8 @@
       <c r="C26" s="4">
         <v>5</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>201</v>
+      <c r="D26" s="2">
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>188</v>
@@ -1516,8 +1522,8 @@
       <c r="C27" s="4">
         <v>5</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>201</v>
+      <c r="D27" s="2">
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>188</v>
@@ -1533,8 +1539,8 @@
       <c r="C28" s="4">
         <v>5</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>201</v>
+      <c r="D28" s="2">
+        <v>9</v>
       </c>
       <c r="E28" t="s">
         <v>188</v>
@@ -1550,8 +1556,8 @@
       <c r="C29" s="4">
         <v>5</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>201</v>
+      <c r="D29" s="2">
+        <v>9</v>
       </c>
       <c r="E29" t="s">
         <v>188</v>
@@ -1567,8 +1573,8 @@
       <c r="C30" s="4">
         <v>10</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>201</v>
+      <c r="D30" s="2">
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>187</v>
@@ -1584,8 +1590,8 @@
       <c r="C31" s="4">
         <v>4.96</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>201</v>
+      <c r="D31" s="2">
+        <v>9</v>
       </c>
       <c r="E31" t="s">
         <v>188</v>
@@ -1601,8 +1607,8 @@
       <c r="C32" s="4">
         <v>9</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>201</v>
+      <c r="D32" s="2">
+        <v>9</v>
       </c>
       <c r="E32" t="s">
         <v>187</v>
@@ -1618,8 +1624,8 @@
       <c r="C33" s="4">
         <v>106.64</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>201</v>
+      <c r="D33" s="2">
+        <v>9</v>
       </c>
       <c r="E33" t="s">
         <v>194</v>
@@ -1635,8 +1641,8 @@
       <c r="C34" s="4">
         <v>183.9</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>201</v>
+      <c r="D34" s="2">
+        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>186</v>
@@ -1652,8 +1658,8 @@
       <c r="C35" s="4">
         <v>375</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>201</v>
+      <c r="D35" s="2">
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>186</v>
@@ -1669,8 +1675,8 @@
       <c r="C36" s="4">
         <v>44</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>201</v>
+      <c r="D36" s="2">
+        <v>9</v>
       </c>
       <c r="E36" t="s">
         <v>186</v>
@@ -1686,8 +1692,8 @@
       <c r="C37" s="4">
         <v>2.23</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>201</v>
+      <c r="D37" s="2">
+        <v>9</v>
       </c>
       <c r="E37" t="s">
         <v>186</v>
@@ -1703,8 +1709,8 @@
       <c r="C38" s="4">
         <v>3</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>201</v>
+      <c r="D38" s="2">
+        <v>9</v>
       </c>
       <c r="E38" t="s">
         <v>187</v>
@@ -1720,8 +1726,8 @@
       <c r="C39" s="4">
         <v>5.9</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>201</v>
+      <c r="D39" s="2">
+        <v>9</v>
       </c>
       <c r="E39" t="s">
         <v>194</v>
@@ -1737,8 +1743,8 @@
       <c r="C40" s="4">
         <v>19.5</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>201</v>
+      <c r="D40" s="2">
+        <v>9</v>
       </c>
       <c r="E40" t="s">
         <v>194</v>
@@ -1754,8 +1760,8 @@
       <c r="C41" s="4">
         <v>12.1</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>201</v>
+      <c r="D41" s="2">
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>194</v>
@@ -1771,8 +1777,8 @@
       <c r="C42" s="4">
         <v>13</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>201</v>
+      <c r="D42" s="2">
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>194</v>
@@ -1786,10 +1792,10 @@
         <v>44</v>
       </c>
       <c r="C43" s="4">
-        <v>80</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>201</v>
+        <v>60</v>
+      </c>
+      <c r="D43" s="2">
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>194</v>
@@ -1805,8 +1811,8 @@
       <c r="C44" s="4">
         <v>175</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>201</v>
+      <c r="D44" s="2">
+        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>194</v>
@@ -1820,10 +1826,10 @@
         <v>46</v>
       </c>
       <c r="C45" s="4">
-        <v>175</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>201</v>
+        <v>225</v>
+      </c>
+      <c r="D45" s="2">
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>194</v>
@@ -1839,8 +1845,8 @@
       <c r="C46" s="4">
         <v>40</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>201</v>
+      <c r="D46" s="2">
+        <v>9</v>
       </c>
       <c r="E46" t="s">
         <v>194</v>
@@ -1856,8 +1862,8 @@
       <c r="C47" s="4">
         <v>100</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>201</v>
+      <c r="D47" s="2">
+        <v>9</v>
       </c>
       <c r="E47" t="s">
         <v>194</v>
@@ -1873,8 +1879,8 @@
       <c r="C48" s="4">
         <v>50</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>201</v>
+      <c r="D48" s="2">
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>194</v>
@@ -1890,8 +1896,8 @@
       <c r="C49" s="4">
         <v>40</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>201</v>
+      <c r="D49" s="2">
+        <v>9</v>
       </c>
       <c r="E49" t="s">
         <v>194</v>
@@ -1907,8 +1913,8 @@
       <c r="C50" s="4">
         <v>18</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>201</v>
+      <c r="D50" s="2">
+        <v>9</v>
       </c>
       <c r="E50" t="s">
         <v>187</v>
@@ -1924,8 +1930,8 @@
       <c r="C51" s="4">
         <v>8</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>201</v>
+      <c r="D51" s="2">
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>191</v>
@@ -1941,8 +1947,8 @@
       <c r="C52" s="4">
         <v>13.8</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>201</v>
+      <c r="D52" s="2">
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>186</v>
@@ -1956,10 +1962,10 @@
         <v>54</v>
       </c>
       <c r="C53" s="4">
-        <v>599</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>201</v>
+        <v>429</v>
+      </c>
+      <c r="D53" s="2">
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>186</v>
@@ -1975,8 +1981,8 @@
       <c r="C54" s="4">
         <v>25</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>201</v>
+      <c r="D54" s="2">
+        <v>9</v>
       </c>
       <c r="E54" t="s">
         <v>186</v>
@@ -1992,8 +1998,8 @@
       <c r="C55" s="4">
         <v>127.8</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>201</v>
+      <c r="D55" s="2">
+        <v>9</v>
       </c>
       <c r="E55" t="s">
         <v>186</v>
@@ -2009,8 +2015,8 @@
       <c r="C56" s="4">
         <v>17.899999999999999</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>201</v>
+      <c r="D56" s="2">
+        <v>9</v>
       </c>
       <c r="E56" t="s">
         <v>186</v>
@@ -2026,8 +2032,8 @@
       <c r="C57" s="4">
         <v>760</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>201</v>
+      <c r="D57" s="2">
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>6</v>
@@ -2041,10 +2047,10 @@
         <v>197</v>
       </c>
       <c r="C58" s="4">
-        <v>320</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>201</v>
+        <v>160</v>
+      </c>
+      <c r="D58" s="2">
+        <v>9</v>
       </c>
       <c r="E58" t="s">
         <v>6</v>
@@ -2060,8 +2066,8 @@
       <c r="C59" s="4">
         <v>657.5</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>201</v>
+      <c r="D59" s="2">
+        <v>9</v>
       </c>
       <c r="E59" t="s">
         <v>6</v>
@@ -2069,16 +2075,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="C60" s="4">
-        <v>577</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>201</v>
+        <v>135</v>
+      </c>
+      <c r="D60" s="2">
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>6</v>
@@ -2086,33 +2092,33 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C61" s="4">
-        <v>2160</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>201</v>
+        <v>577</v>
+      </c>
+      <c r="D61" s="2">
+        <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="4">
-        <v>100.04900000000001</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>201</v>
+        <v>1980</v>
+      </c>
+      <c r="D62" s="2">
+        <v>9</v>
       </c>
       <c r="E62" t="s">
         <v>186</v>
@@ -2120,16 +2126,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" s="4">
-        <v>15.55</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>201</v>
+        <v>100.04900000000001</v>
+      </c>
+      <c r="D63" s="2">
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>186</v>
@@ -2137,50 +2143,50 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" s="4">
-        <v>21.7</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>201</v>
+        <v>15.55</v>
+      </c>
+      <c r="D64" s="2">
+        <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C65" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>201</v>
+        <v>21.7</v>
+      </c>
+      <c r="D65" s="2">
+        <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>201</v>
+        <v>2.5</v>
+      </c>
+      <c r="D66" s="2">
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>194</v>
@@ -2188,33 +2194,33 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" s="4">
-        <v>60.8</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>201</v>
+        <v>0.7</v>
+      </c>
+      <c r="D67" s="2">
+        <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" s="4">
-        <v>185</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>201</v>
+        <v>60.8</v>
+      </c>
+      <c r="D68" s="2">
+        <v>9</v>
       </c>
       <c r="E68" t="s">
         <v>186</v>
@@ -2222,16 +2228,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="C69" s="4">
-        <v>190</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>201</v>
+        <v>370</v>
+      </c>
+      <c r="D69" s="2">
+        <v>9</v>
       </c>
       <c r="E69" t="s">
         <v>186</v>
@@ -2239,16 +2245,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C70" s="4">
-        <v>31.83</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>201</v>
+        <v>185</v>
+      </c>
+      <c r="D70" s="2">
+        <v>9</v>
       </c>
       <c r="E70" t="s">
         <v>186</v>
@@ -2256,16 +2262,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C71" s="4">
-        <v>151.4</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
+      </c>
+      <c r="D71" s="2">
+        <v>9</v>
       </c>
       <c r="E71" t="s">
         <v>186</v>
@@ -2273,16 +2279,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C72" s="4">
-        <v>36</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>201</v>
+        <v>31.83</v>
+      </c>
+      <c r="D72" s="2">
+        <v>9</v>
       </c>
       <c r="E72" t="s">
         <v>186</v>
@@ -2290,16 +2296,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C73" s="4">
-        <v>11</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>201</v>
+        <v>151.4</v>
+      </c>
+      <c r="D73" s="2">
+        <v>9</v>
       </c>
       <c r="E73" t="s">
         <v>186</v>
@@ -2307,169 +2313,169 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C74" s="4">
-        <v>54</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>201</v>
+        <v>36</v>
+      </c>
+      <c r="D74" s="2">
+        <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C75" s="4">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>201</v>
+        <v>11</v>
+      </c>
+      <c r="D75" s="2">
+        <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C76" s="4">
-        <v>19.559999999999999</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>201</v>
+        <v>54</v>
+      </c>
+      <c r="D76" s="2">
+        <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C77" s="4">
-        <v>9.65</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>201</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D77" s="2">
+        <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C78" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>201</v>
+        <v>19.559999999999999</v>
+      </c>
+      <c r="D78" s="2">
+        <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>404</v>
+        <v>174</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C79" s="4">
-        <v>25</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>201</v>
+        <v>9.65</v>
+      </c>
+      <c r="D79" s="2">
+        <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>870</v>
+        <v>186</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C80" s="4">
-        <v>13</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>201</v>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D80" s="2">
+        <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>936</v>
+        <v>404</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C81" s="4">
-        <v>5</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D81" s="2">
+        <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>1494</v>
+        <v>785</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="C82" s="4">
-        <v>329.4</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D82" s="2">
+        <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>1610</v>
+        <v>870</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C83" s="4">
-        <v>90.6</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>201</v>
+        <v>13</v>
+      </c>
+      <c r="D83" s="2">
+        <v>9</v>
       </c>
       <c r="E83" t="s">
         <v>186</v>
@@ -2477,84 +2483,84 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>1961</v>
+        <v>936</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C84" s="4">
-        <v>17</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>201</v>
+        <v>5</v>
+      </c>
+      <c r="D84" s="2">
+        <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>2215</v>
+        <v>1494</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C85" s="4">
-        <v>24.658000000000001</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>201</v>
+        <v>329.4</v>
+      </c>
+      <c r="D85" s="2">
+        <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>2223</v>
+        <v>1610</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C86" s="4">
-        <v>211</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>201</v>
+        <v>90.6</v>
+      </c>
+      <c r="D86" s="2">
+        <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>2572</v>
+        <v>1961</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C87" s="4">
-        <v>25</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>201</v>
+        <v>17</v>
+      </c>
+      <c r="D87" s="2">
+        <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>2728</v>
+        <v>2215</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C88" s="4">
-        <v>131.4</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>201</v>
+        <v>24.658000000000001</v>
+      </c>
+      <c r="D88" s="2">
+        <v>9</v>
       </c>
       <c r="E88" t="s">
         <v>194</v>
@@ -2562,33 +2568,33 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>2794</v>
+        <v>2223</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C89" s="4">
-        <v>100</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>201</v>
+        <v>211</v>
+      </c>
+      <c r="D89" s="2">
+        <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>2833</v>
+        <v>2572</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C90" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D90" s="2">
+        <v>9</v>
       </c>
       <c r="E90" t="s">
         <v>194</v>
@@ -2596,152 +2602,152 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>3202</v>
+        <v>2728</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C91" s="4">
-        <v>7.9</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>201</v>
+        <v>131.4</v>
+      </c>
+      <c r="D91" s="2">
+        <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>3203</v>
+        <v>2794</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C92" s="4">
-        <v>28</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>201</v>
+        <v>100</v>
+      </c>
+      <c r="D92" s="2">
+        <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>3204</v>
+        <v>2833</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C93" s="4">
-        <v>301</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>201</v>
+        <v>30.7</v>
+      </c>
+      <c r="D93" s="2">
+        <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>3220</v>
+        <v>3202</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C94" s="4">
-        <v>21</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>201</v>
+        <v>7.9</v>
+      </c>
+      <c r="D94" s="2">
+        <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>3643</v>
+        <v>3203</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C95" s="4">
-        <v>25</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>201</v>
+        <v>28</v>
+      </c>
+      <c r="D95" s="2">
+        <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>3932</v>
+        <v>3204</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C96" s="4">
-        <v>35</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>201</v>
+        <v>301</v>
+      </c>
+      <c r="D96" s="2">
+        <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>3933</v>
+        <v>3220</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C97" s="4">
-        <v>55</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>201</v>
+        <v>21</v>
+      </c>
+      <c r="D97" s="2">
+        <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>3935</v>
+        <v>3643</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C98" s="4">
         <v>25</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>201</v>
+      <c r="D98" s="2">
+        <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>3936</v>
+        <v>3932</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C99" s="4">
-        <v>25</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>201</v>
+        <v>35</v>
+      </c>
+      <c r="D99" s="2">
+        <v>9</v>
       </c>
       <c r="E99" t="s">
         <v>194</v>
@@ -2749,16 +2755,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>3937</v>
+        <v>3933</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C100" s="4">
-        <v>20</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>201</v>
+        <v>55</v>
+      </c>
+      <c r="D100" s="2">
+        <v>9</v>
       </c>
       <c r="E100" t="s">
         <v>194</v>
@@ -2766,33 +2772,33 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>3962</v>
+        <v>3935</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C101" s="4">
-        <v>135.82300000000001</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D101" s="2">
+        <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>4045</v>
+        <v>3936</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C102" s="4">
-        <v>13.3</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D102" s="2">
+        <v>9</v>
       </c>
       <c r="E102" t="s">
         <v>194</v>
@@ -2800,203 +2806,203 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>4047</v>
+        <v>3937</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C103" s="4">
-        <v>20.887</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>201</v>
+        <v>20</v>
+      </c>
+      <c r="D103" s="2">
+        <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>4106</v>
+        <v>3962</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C104" s="4">
-        <v>50</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>201</v>
+        <v>135.82300000000001</v>
+      </c>
+      <c r="D104" s="2">
+        <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>4161</v>
+        <v>4045</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C105" s="4">
-        <v>94</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>201</v>
+        <v>13.3</v>
+      </c>
+      <c r="D105" s="2">
+        <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>4256</v>
+        <v>4047</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C106" s="4">
-        <v>40</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>201</v>
+        <v>20.887</v>
+      </c>
+      <c r="D106" s="2">
+        <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>4319</v>
+        <v>4106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C107" s="4">
-        <v>30</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D107" s="2">
+        <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>4329</v>
+        <v>4161</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C108" s="4">
-        <v>40</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>201</v>
+        <v>94</v>
+      </c>
+      <c r="D108" s="2">
+        <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>4377</v>
+        <v>4256</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C109" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>201</v>
+        <v>40</v>
+      </c>
+      <c r="D109" s="2">
+        <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>4477</v>
+        <v>4319</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C110" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>201</v>
+        <v>30</v>
+      </c>
+      <c r="D110" s="2">
+        <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>4478</v>
+        <v>4329</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C111" s="4">
-        <v>100</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>201</v>
+        <v>40</v>
+      </c>
+      <c r="D111" s="2">
+        <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>4478</v>
+        <v>4377</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C112" s="4">
-        <v>800</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>201</v>
+        <v>29.5</v>
+      </c>
+      <c r="D112" s="2">
+        <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>4478</v>
+        <v>4477</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C113" s="4">
-        <v>2100</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>201</v>
+        <v>18.8</v>
+      </c>
+      <c r="D113" s="2">
+        <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C114" s="4">
-        <v>150</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>201</v>
+        <v>800</v>
+      </c>
+      <c r="D114" s="2">
+        <v>9</v>
       </c>
       <c r="E114" t="s">
         <v>193</v>
@@ -3004,50 +3010,50 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>4729</v>
+        <v>4478</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C115" s="4">
-        <v>318.8</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>201</v>
+        <v>2100</v>
+      </c>
+      <c r="D115" s="2">
+        <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>4730</v>
+        <v>4479</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C116" s="4">
-        <v>144</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>201</v>
+        <v>150</v>
+      </c>
+      <c r="D116" s="2">
+        <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>4799</v>
+        <v>4729</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C117" s="4">
-        <v>218.01</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>201</v>
+        <v>318.8</v>
+      </c>
+      <c r="D117" s="2">
+        <v>9</v>
       </c>
       <c r="E117" t="s">
         <v>194</v>
@@ -3055,33 +3061,33 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>4848</v>
+        <v>4730</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C118" s="4">
-        <v>25</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>201</v>
+        <v>144</v>
+      </c>
+      <c r="D118" s="2">
+        <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>5022</v>
+        <v>4799</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C119" s="4">
-        <v>25</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>201</v>
+        <v>218.01</v>
+      </c>
+      <c r="D119" s="2">
+        <v>9</v>
       </c>
       <c r="E119" t="s">
         <v>194</v>
@@ -3089,50 +3095,50 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>5087</v>
+        <v>4848</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="C120" s="4">
-        <v>50</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D120" s="2">
+        <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>5117</v>
+        <v>5022</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C121" s="4">
-        <v>38</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D121" s="2">
+        <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>5120</v>
+        <v>5087</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C122" s="4">
-        <v>25</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D122" s="2">
+        <v>9</v>
       </c>
       <c r="E122" t="s">
         <v>194</v>
@@ -3140,16 +3146,16 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>5187</v>
+        <v>5117</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C123" s="4">
-        <v>190</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>201</v>
+        <v>38</v>
+      </c>
+      <c r="D123" s="2">
+        <v>9</v>
       </c>
       <c r="E123" t="s">
         <v>186</v>
@@ -3157,16 +3163,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>5260</v>
+        <v>5120</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="C124" s="4">
-        <v>5</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D124" s="2">
+        <v>9</v>
       </c>
       <c r="E124" t="s">
         <v>194</v>
@@ -3174,16 +3180,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>5373</v>
+        <v>5187</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C125" s="4">
-        <v>20</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>201</v>
+        <v>190</v>
+      </c>
+      <c r="D125" s="2">
+        <v>9</v>
       </c>
       <c r="E125" t="s">
         <v>186</v>
@@ -3191,50 +3197,50 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>5736</v>
+        <v>5260</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C126" s="4">
         <v>5</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>201</v>
+      <c r="D126" s="2">
+        <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>5741</v>
+        <v>5373</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C127" s="4">
-        <v>5</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>201</v>
+        <v>20</v>
+      </c>
+      <c r="D127" s="2">
+        <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>5742</v>
+        <v>5736</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C128" s="4">
-        <v>19.2</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>201</v>
+        <v>5</v>
+      </c>
+      <c r="D128" s="2">
+        <v>9</v>
       </c>
       <c r="E128" t="s">
         <v>186</v>
@@ -3242,50 +3248,50 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>5743</v>
+        <v>5741</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C129" s="4">
-        <v>2</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>201</v>
+        <v>5</v>
+      </c>
+      <c r="D129" s="2">
+        <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>5747</v>
+        <v>5742</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C130" s="4">
-        <v>5.98</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>201</v>
+        <v>19.2</v>
+      </c>
+      <c r="D130" s="2">
+        <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>5748</v>
+        <v>5743</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C131" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>201</v>
+        <v>2</v>
+      </c>
+      <c r="D131" s="2">
+        <v>9</v>
       </c>
       <c r="E131" t="s">
         <v>186</v>
@@ -3293,67 +3299,67 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>5750</v>
+        <v>5747</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C132" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>201</v>
+        <v>5.98</v>
+      </c>
+      <c r="D132" s="2">
+        <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>5796</v>
+        <v>5748</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C133" s="4">
-        <v>50</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>201</v>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D133" s="2">
+        <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>5796</v>
+        <v>5750</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C134" s="4">
-        <v>150</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>201</v>
+        <v>28.7</v>
+      </c>
+      <c r="D134" s="2">
+        <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>5797</v>
+        <v>5796</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C135" s="4">
-        <v>100</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D135" s="2">
+        <v>9</v>
       </c>
       <c r="E135" t="s">
         <v>193</v>
@@ -3361,16 +3367,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>5797</v>
+        <v>5796</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C136" s="4">
-        <v>400</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>201</v>
+        <v>150</v>
+      </c>
+      <c r="D136" s="2">
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>193</v>
@@ -3384,10 +3390,10 @@
         <v>130</v>
       </c>
       <c r="C137" s="4">
-        <v>800</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>201</v>
+        <v>100</v>
+      </c>
+      <c r="D137" s="2">
+        <v>9</v>
       </c>
       <c r="E137" t="s">
         <v>193</v>
@@ -3395,33 +3401,33 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>5809</v>
+        <v>5797</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C138" s="4">
-        <v>359.4</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>201</v>
+        <v>800</v>
+      </c>
+      <c r="D138" s="2">
+        <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>5810</v>
+        <v>5809</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C139" s="4">
-        <v>1260</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>201</v>
+        <v>359.4</v>
+      </c>
+      <c r="D139" s="2">
+        <v>9</v>
       </c>
       <c r="E139" t="s">
         <v>189</v>
@@ -3429,16 +3435,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>5811</v>
+        <v>5810</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C140" s="4">
-        <v>160.30000000000001</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>201</v>
+        <v>1260</v>
+      </c>
+      <c r="D140" s="2">
+        <v>9</v>
       </c>
       <c r="E140" t="s">
         <v>189</v>
@@ -3446,16 +3452,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C141" s="4">
-        <v>159.80000000000001</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>201</v>
+        <v>160.30000000000001</v>
+      </c>
+      <c r="D141" s="2">
+        <v>9</v>
       </c>
       <c r="E141" t="s">
         <v>189</v>
@@ -3463,36 +3469,36 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>5856</v>
+        <v>5812</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C142" s="4">
-        <v>110</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>201</v>
+        <v>159.80000000000001</v>
+      </c>
+      <c r="D142" s="2">
+        <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>6505</v>
+        <v>5856</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C143" s="4">
-        <v>50</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>201</v>
+        <v>110</v>
+      </c>
+      <c r="D143" s="2">
+        <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -3503,10 +3509,10 @@
         <v>136</v>
       </c>
       <c r="C144" s="4">
-        <v>100</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D144" s="2">
+        <v>9</v>
       </c>
       <c r="E144" t="s">
         <v>193</v>
@@ -3514,16 +3520,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>6506</v>
+        <v>6505</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C145" s="4">
-        <v>150</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>201</v>
+        <v>100</v>
+      </c>
+      <c r="D145" s="2">
+        <v>9</v>
       </c>
       <c r="E145" t="s">
         <v>193</v>
@@ -3537,10 +3543,10 @@
         <v>137</v>
       </c>
       <c r="C146" s="4">
-        <v>450</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>201</v>
+        <v>150</v>
+      </c>
+      <c r="D146" s="2">
+        <v>9</v>
       </c>
       <c r="E146" t="s">
         <v>193</v>
@@ -3556,8 +3562,8 @@
       <c r="C147" s="4">
         <v>800</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>201</v>
+      <c r="D147" s="2">
+        <v>9</v>
       </c>
       <c r="E147" t="s">
         <v>193</v>
@@ -3573,8 +3579,8 @@
       <c r="C148" s="4">
         <v>100</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>201</v>
+      <c r="D148" s="2">
+        <v>9</v>
       </c>
       <c r="E148" t="s">
         <v>193</v>
@@ -3590,8 +3596,8 @@
       <c r="C149" s="4">
         <v>400</v>
       </c>
-      <c r="D149" s="3" t="s">
-        <v>201</v>
+      <c r="D149" s="2">
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>193</v>
@@ -3607,8 +3613,8 @@
       <c r="C150" s="4">
         <v>14.9</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>201</v>
+      <c r="D150" s="2">
+        <v>9</v>
       </c>
       <c r="E150" t="s">
         <v>193</v>
@@ -3624,8 +3630,8 @@
       <c r="C151" s="4">
         <v>150</v>
       </c>
-      <c r="D151" s="3" t="s">
-        <v>201</v>
+      <c r="D151" s="2">
+        <v>9</v>
       </c>
       <c r="E151" t="s">
         <v>193</v>
@@ -3641,8 +3647,8 @@
       <c r="C152" s="4">
         <v>82.8</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>201</v>
+      <c r="D152" s="2">
+        <v>9</v>
       </c>
       <c r="E152" t="s">
         <v>193</v>
@@ -3658,8 +3664,8 @@
       <c r="C153" s="4">
         <v>50</v>
       </c>
-      <c r="D153" s="3" t="s">
-        <v>201</v>
+      <c r="D153" s="2">
+        <v>9</v>
       </c>
       <c r="E153" t="s">
         <v>193</v>
@@ -3675,8 +3681,8 @@
       <c r="C154" s="4">
         <v>100</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>201</v>
+      <c r="D154" s="2">
+        <v>9</v>
       </c>
       <c r="E154" t="s">
         <v>193</v>
@@ -3692,8 +3698,8 @@
       <c r="C155" s="4">
         <v>300</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>201</v>
+      <c r="D155" s="2">
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>193</v>
@@ -3709,8 +3715,8 @@
       <c r="C156" s="4">
         <v>24.998999999999999</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>201</v>
+      <c r="D156" s="2">
+        <v>9</v>
       </c>
       <c r="E156" t="s">
         <v>193</v>
@@ -3726,8 +3732,8 @@
       <c r="C157" s="4">
         <v>100</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>201</v>
+      <c r="D157" s="2">
+        <v>9</v>
       </c>
       <c r="E157" t="s">
         <v>193</v>
@@ -3743,8 +3749,8 @@
       <c r="C158" s="4">
         <v>250</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>201</v>
+      <c r="D158" s="2">
+        <v>9</v>
       </c>
       <c r="E158" t="s">
         <v>193</v>
@@ -3760,8 +3766,8 @@
       <c r="C159" s="4">
         <v>150</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>201</v>
+      <c r="D159" s="2">
+        <v>9</v>
       </c>
       <c r="E159" t="s">
         <v>186</v>
@@ -3775,10 +3781,10 @@
         <v>146</v>
       </c>
       <c r="C160" s="4">
-        <v>2850</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>201</v>
+        <v>4750</v>
+      </c>
+      <c r="D160" s="2">
+        <v>9</v>
       </c>
       <c r="E160" t="s">
         <v>6</v>
@@ -3794,8 +3800,8 @@
       <c r="C161" s="4">
         <v>540</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>201</v>
+      <c r="D161" s="2">
+        <v>9</v>
       </c>
       <c r="E161" t="s">
         <v>186</v>
@@ -3811,8 +3817,8 @@
       <c r="C162" s="4">
         <v>36.6</v>
       </c>
-      <c r="D162" s="3" t="s">
-        <v>201</v>
+      <c r="D162" s="2">
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>186</v>
@@ -3828,8 +3834,8 @@
       <c r="C163" s="4">
         <v>25</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>201</v>
+      <c r="D163" s="2">
+        <v>9</v>
       </c>
       <c r="E163" t="s">
         <v>194</v>
@@ -3845,8 +3851,8 @@
       <c r="C164" s="4">
         <v>18</v>
       </c>
-      <c r="D164" s="3" t="s">
-        <v>201</v>
+      <c r="D164" s="2">
+        <v>9</v>
       </c>
       <c r="E164" t="s">
         <v>187</v>
@@ -3860,10 +3866,10 @@
         <v>150</v>
       </c>
       <c r="C165" s="4">
-        <v>18</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>201</v>
+        <v>36</v>
+      </c>
+      <c r="D165" s="2">
+        <v>9</v>
       </c>
       <c r="E165" t="s">
         <v>187</v>
@@ -3877,10 +3883,10 @@
         <v>151</v>
       </c>
       <c r="C166" s="4">
-        <v>1900</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>201</v>
+        <v>1710</v>
+      </c>
+      <c r="D166" s="2">
+        <v>9</v>
       </c>
       <c r="E166" t="s">
         <v>186</v>
@@ -3896,8 +3902,8 @@
       <c r="C167" s="4">
         <v>2</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>201</v>
+      <c r="D167" s="2">
+        <v>9</v>
       </c>
       <c r="E167" t="s">
         <v>194</v>
@@ -3913,8 +3919,8 @@
       <c r="C168" s="4">
         <v>25</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>201</v>
+      <c r="D168" s="2">
+        <v>9</v>
       </c>
       <c r="E168" t="s">
         <v>194</v>
@@ -3930,8 +3936,8 @@
       <c r="C169" s="4">
         <v>180</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>201</v>
+      <c r="D169" s="2">
+        <v>9</v>
       </c>
       <c r="E169" t="s">
         <v>189</v>
@@ -3947,8 +3953,8 @@
       <c r="C170" s="4">
         <v>2700</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>201</v>
+      <c r="D170" s="2">
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>189</v>
@@ -3964,8 +3970,8 @@
       <c r="C171" s="4">
         <v>3060</v>
       </c>
-      <c r="D171" s="3" t="s">
-        <v>201</v>
+      <c r="D171" s="2">
+        <v>9</v>
       </c>
       <c r="E171" t="s">
         <v>189</v>
@@ -3981,8 +3987,8 @@
       <c r="C172" s="4">
         <v>897</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>201</v>
+      <c r="D172" s="2">
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>189</v>
@@ -3998,8 +4004,8 @@
       <c r="C173" s="4">
         <v>540</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>201</v>
+      <c r="D173" s="2">
+        <v>9</v>
       </c>
       <c r="E173" t="s">
         <v>189</v>
@@ -4015,8 +4021,8 @@
       <c r="C174" s="4">
         <v>705</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>201</v>
+      <c r="D174" s="2">
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>189</v>
@@ -4032,8 +4038,8 @@
       <c r="C175" s="4">
         <v>1980</v>
       </c>
-      <c r="D175" s="3" t="s">
-        <v>201</v>
+      <c r="D175" s="2">
+        <v>9</v>
       </c>
       <c r="E175" t="s">
         <v>189</v>
@@ -4049,8 +4055,8 @@
       <c r="C176" s="4">
         <v>300</v>
       </c>
-      <c r="D176" s="3" t="s">
-        <v>201</v>
+      <c r="D176" s="2">
+        <v>9</v>
       </c>
       <c r="E176" t="s">
         <v>189</v>
@@ -4066,8 +4072,8 @@
       <c r="C177" s="4">
         <v>2700</v>
       </c>
-      <c r="D177" s="3" t="s">
-        <v>201</v>
+      <c r="D177" s="2">
+        <v>9</v>
       </c>
       <c r="E177" t="s">
         <v>189</v>
@@ -4081,10 +4087,10 @@
         <v>159</v>
       </c>
       <c r="C178" s="4">
-        <v>360</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>201</v>
+        <v>180</v>
+      </c>
+      <c r="D178" s="2">
+        <v>9</v>
       </c>
       <c r="E178" t="s">
         <v>189</v>
@@ -4098,10 +4104,10 @@
         <v>160</v>
       </c>
       <c r="C179" s="4">
-        <v>180</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>201</v>
+        <v>1440</v>
+      </c>
+      <c r="D179" s="2">
+        <v>9</v>
       </c>
       <c r="E179" t="s">
         <v>189</v>
@@ -4109,16 +4115,16 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>11379</v>
+        <v>11380</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C180" s="4">
-        <v>1440</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>201</v>
+        <v>180</v>
+      </c>
+      <c r="D180" s="2">
+        <v>9</v>
       </c>
       <c r="E180" t="s">
         <v>189</v>
@@ -4126,67 +4132,67 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>11380</v>
+        <v>11612</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C181" s="4">
-        <v>180</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>201</v>
+        <v>25</v>
+      </c>
+      <c r="D181" s="2">
+        <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>11612</v>
+        <v>11849</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C182" s="4">
-        <v>25</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D182" s="2">
+        <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>11849</v>
+        <v>12710</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C183" s="4">
-        <v>50</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>201</v>
+        <v>2.5</v>
+      </c>
+      <c r="D183" s="2">
+        <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>12710</v>
+        <v>12711</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C184" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>201</v>
+        <v>1</v>
+      </c>
+      <c r="D184" s="2">
+        <v>9</v>
       </c>
       <c r="E184" t="s">
         <v>189</v>
@@ -4194,16 +4200,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>12711</v>
+        <v>12712</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C185" s="4">
-        <v>1</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>201</v>
+        <v>0.06</v>
+      </c>
+      <c r="D185" s="2">
+        <v>9</v>
       </c>
       <c r="E185" t="s">
         <v>189</v>
@@ -4211,16 +4217,16 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>12712</v>
+        <v>12713</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C186" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>201</v>
+        <v>1</v>
+      </c>
+      <c r="D186" s="2">
+        <v>9</v>
       </c>
       <c r="E186" t="s">
         <v>189</v>
@@ -4228,50 +4234,50 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>12713</v>
+        <v>12714</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C187" s="4">
-        <v>1</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>201</v>
+        <v>0.05</v>
+      </c>
+      <c r="D187" s="2">
+        <v>9</v>
       </c>
       <c r="E187" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>12714</v>
+        <v>12715</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C188" s="4">
         <v>0.05</v>
       </c>
-      <c r="D188" s="3" t="s">
-        <v>201</v>
+      <c r="D188" s="2">
+        <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>12715</v>
+        <v>12716</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C189" s="4">
         <v>0.05</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>201</v>
+      <c r="D189" s="2">
+        <v>9</v>
       </c>
       <c r="E189" t="s">
         <v>189</v>
@@ -4279,16 +4285,16 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>12716</v>
+        <v>12717</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C190" s="4">
         <v>0.05</v>
       </c>
-      <c r="D190" s="3" t="s">
-        <v>201</v>
+      <c r="D190" s="2">
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>189</v>
@@ -4296,16 +4302,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>12717</v>
+        <v>12718</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C191" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>201</v>
+        <v>1</v>
+      </c>
+      <c r="D191" s="2">
+        <v>9</v>
       </c>
       <c r="E191" t="s">
         <v>189</v>
@@ -4313,33 +4319,33 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>12718</v>
+        <v>12924</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C192" s="4">
-        <v>1</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>201</v>
+        <v>20</v>
+      </c>
+      <c r="D192" s="2">
+        <v>9</v>
       </c>
       <c r="E192" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>12924</v>
+        <v>14753</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C193" s="4">
-        <v>20</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>201</v>
+        <v>711</v>
+      </c>
+      <c r="D193" s="2">
+        <v>9</v>
       </c>
       <c r="E193" t="s">
         <v>186</v>
@@ -4347,16 +4353,16 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>14753</v>
+        <v>14925</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C194" s="4">
-        <v>711</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>201</v>
+        <v>850</v>
+      </c>
+      <c r="D194" s="2">
+        <v>9</v>
       </c>
       <c r="E194" t="s">
         <v>186</v>
@@ -4364,33 +4370,33 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>14925</v>
+        <v>15176</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C195" s="4">
-        <v>1020</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>201</v>
+        <v>150</v>
+      </c>
+      <c r="D195" s="2">
+        <v>9</v>
       </c>
       <c r="E195" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>15176</v>
+        <v>15178</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C196" s="4">
         <v>150</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>201</v>
+      <c r="D196" s="2">
+        <v>9</v>
       </c>
       <c r="E196" t="s">
         <v>194</v>
@@ -4398,16 +4404,16 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>15178</v>
+        <v>15180</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C197" s="4">
-        <v>150</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>201</v>
+        <v>250</v>
+      </c>
+      <c r="D197" s="2">
+        <v>9</v>
       </c>
       <c r="E197" t="s">
         <v>194</v>
@@ -4415,16 +4421,16 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>15180</v>
+        <v>15181</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C198" s="4">
-        <v>250</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
+      </c>
+      <c r="D198" s="2">
+        <v>9</v>
       </c>
       <c r="E198" t="s">
         <v>194</v>
@@ -4432,16 +4438,16 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>15181</v>
+        <v>15182</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C199" s="4">
         <v>210</v>
       </c>
-      <c r="D199" s="3" t="s">
-        <v>201</v>
+      <c r="D199" s="2">
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>194</v>
@@ -4449,16 +4455,16 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>15182</v>
+        <v>15183</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C200" s="4">
-        <v>210</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>201</v>
+        <v>1540</v>
+      </c>
+      <c r="D200" s="2">
+        <v>9</v>
       </c>
       <c r="E200" t="s">
         <v>194</v>
@@ -4466,16 +4472,16 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>15183</v>
+        <v>15184</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C201" s="4">
-        <v>1540</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="D201" s="2">
+        <v>9</v>
       </c>
       <c r="E201" t="s">
         <v>194</v>
@@ -4483,16 +4489,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>15184</v>
+        <v>15185</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C202" s="4">
-        <v>200</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="D202" s="2">
+        <v>9</v>
       </c>
       <c r="E202" t="s">
         <v>194</v>
@@ -4500,16 +4506,16 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
-        <v>15185</v>
+        <v>15187</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C203" s="4">
-        <v>50</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>201</v>
+        <v>41.5</v>
+      </c>
+      <c r="D203" s="2">
+        <v>9</v>
       </c>
       <c r="E203" t="s">
         <v>194</v>
@@ -4523,10 +4529,10 @@
         <v>183</v>
       </c>
       <c r="C204" s="4">
-        <v>41.5</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>201</v>
+        <v>125</v>
+      </c>
+      <c r="D204" s="2">
+        <v>9</v>
       </c>
       <c r="E204" t="s">
         <v>194</v>
@@ -4534,19 +4540,19 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
-        <v>15187</v>
+        <v>16336</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C205" s="4">
-        <v>125</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>201</v>
+        <v>180</v>
+      </c>
+      <c r="D205" s="2">
+        <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
@@ -4557,10 +4563,10 @@
         <v>184</v>
       </c>
       <c r="C206" s="4">
-        <v>180</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>201</v>
+        <v>3240</v>
+      </c>
+      <c r="D206" s="2">
+        <v>9</v>
       </c>
       <c r="E206" t="s">
         <v>189</v>
@@ -4568,16 +4574,16 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
-        <v>16336</v>
+        <v>16684</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C207" s="4">
-        <v>3240</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>201</v>
+        <v>360</v>
+      </c>
+      <c r="D207" s="2">
+        <v>9</v>
       </c>
       <c r="E207" t="s">
         <v>189</v>
@@ -4591,31 +4597,20 @@
         <v>185</v>
       </c>
       <c r="C208" s="4">
-        <v>540</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>201</v>
+        <v>2340</v>
+      </c>
+      <c r="D208" s="2">
+        <v>9</v>
       </c>
       <c r="E208" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C209" s="4">
-        <v>2340</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E209" t="s">
-        <v>189</v>
-      </c>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="2"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="4"/>
+      <c r="D209" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data-source/ESTOQUEQUIMICOS.xlsx
+++ b/data-source/ESTOQUEQUIMICOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51B4CEC-D095-4C4A-B940-5EDEFE5818C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3DD17542-BBA7-45E6-A128-B4D037E0B204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B1EAA45-9E5E-4795-87B8-F70C107CD20B}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="1092" windowWidth="20736" windowHeight="11148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="202">
   <si>
     <t>Produto</t>
   </si>
@@ -246,9 +246,6 @@
     <t>RESINA STAHL 4769</t>
   </si>
   <si>
-    <t>RESINA STAHL 10088</t>
-  </si>
-  <si>
     <t>RESINA STAHL 16194</t>
   </si>
   <si>
@@ -624,9 +621,6 @@
     <t>PIGMENTO NACIONAL</t>
   </si>
   <si>
-    <t>RESINA STAHL 16106</t>
-  </si>
-  <si>
     <t>PIGMENTO DIKKA AZUL 153/049</t>
   </si>
   <si>
@@ -636,9 +630,6 @@
     <t>PIGMENTO STANLUX SILVER R 4112</t>
   </si>
   <si>
-    <t>RESINA NOVOTEX - AL233</t>
-  </si>
-  <si>
     <t>RESINA LR206M-3 (AMERICA ASIA)</t>
   </si>
   <si>
@@ -648,10 +639,10 @@
     <t>SOLVENTE ALCOOL ETILICO</t>
   </si>
   <si>
-    <t>RESINA STAHL 4715</t>
-  </si>
-  <si>
     <t>BC 100 SILVER WHITE 10 - BRASCHEMICAL</t>
+  </si>
+  <si>
+    <t>RESINA LARITHANE AL 233</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1075,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1101,171 +1092,171 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4">
-        <v>205</v>
+        <v>172.5</v>
       </c>
       <c r="D3" s="2">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4">
-        <v>172.5</v>
+        <v>130</v>
       </c>
       <c r="D4" s="2">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2">
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>194</v>
       </c>
       <c r="C6" s="4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4">
-        <v>40</v>
+        <v>13.3</v>
       </c>
       <c r="D7" s="2">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>13.3</v>
+        <v>180</v>
       </c>
       <c r="D8" s="2">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>180</v>
+        <v>470</v>
       </c>
       <c r="D9" s="2">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="D10" s="2">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4">
-        <v>410</v>
+        <v>1833.8610000000001</v>
       </c>
       <c r="D11" s="2">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>2733.8609999999999</v>
+        <v>372</v>
       </c>
       <c r="D12" s="2">
         <v>9</v>
@@ -1276,183 +1267,183 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4">
-        <v>372</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2">
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D14" s="2">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4">
-        <v>36</v>
+        <v>1.4</v>
       </c>
       <c r="D15" s="2">
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4">
-        <v>1.4</v>
+        <v>0.89</v>
       </c>
       <c r="D16" s="2">
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4">
-        <v>0.89</v>
+        <v>101.7</v>
       </c>
       <c r="D17" s="2">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4">
-        <v>101.7</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" s="4">
-        <v>95</v>
+        <v>2.85</v>
       </c>
       <c r="D19" s="2">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4">
-        <v>2.85</v>
+        <v>0.65</v>
       </c>
       <c r="D20" s="2">
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4">
-        <v>0.65</v>
+        <v>2.6</v>
       </c>
       <c r="D21" s="2">
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="D22" s="2">
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" s="4">
-        <v>7.6</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="D23" s="2">
         <v>9</v>
@@ -1463,27 +1454,27 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" s="4">
-        <v>4.8899999999999997</v>
+        <v>5</v>
       </c>
       <c r="D24" s="2">
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" s="4">
         <v>5</v>
@@ -1492,15 +1483,15 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4">
         <v>5</v>
@@ -1509,15 +1500,15 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" s="4">
         <v>5</v>
@@ -1526,15 +1517,15 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" s="4">
         <v>5</v>
@@ -1543,35 +1534,35 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2">
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" s="4">
-        <v>10</v>
+        <v>4.96</v>
       </c>
       <c r="D30" s="2">
         <v>9</v>
@@ -1582,115 +1573,115 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4">
-        <v>4.96</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2">
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4">
-        <v>9</v>
+        <v>106.64</v>
       </c>
       <c r="D32" s="2">
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C33" s="4">
-        <v>106.64</v>
+        <v>183.9</v>
       </c>
       <c r="D33" s="2">
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" s="4">
-        <v>183.9</v>
+        <v>375</v>
       </c>
       <c r="D34" s="2">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35" s="4">
-        <v>375</v>
+        <v>44</v>
       </c>
       <c r="D35" s="2">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36" s="4">
-        <v>44</v>
+        <v>2.23</v>
       </c>
       <c r="D36" s="2">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37" s="4">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="D37" s="2">
         <v>9</v>
@@ -1701,336 +1692,336 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38" s="4">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="D38" s="2">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" s="4">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="D39" s="2">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C40" s="4">
-        <v>19.5</v>
+        <v>12.1</v>
       </c>
       <c r="D40" s="2">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C41" s="4">
-        <v>12.1</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2">
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C42" s="4">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D42" s="2">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C43" s="4">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="D43" s="2">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C44" s="4">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="D44" s="2">
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C45" s="4">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2">
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C46" s="4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D46" s="2">
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C47" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D47" s="2">
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D48" s="2">
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C49" s="4">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D49" s="2">
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C50" s="4">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" s="4">
-        <v>8</v>
+        <v>13.8</v>
       </c>
       <c r="D51" s="2">
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C52" s="4">
-        <v>13.8</v>
+        <v>170</v>
       </c>
       <c r="D52" s="2">
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" s="4">
-        <v>429</v>
+        <v>25</v>
       </c>
       <c r="D53" s="2">
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C54" s="4">
-        <v>25</v>
+        <v>127.8</v>
       </c>
       <c r="D54" s="2">
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C55" s="4">
-        <v>127.8</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D55" s="2">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C56" s="4">
-        <v>17.899999999999999</v>
+        <v>380</v>
       </c>
       <c r="D56" s="2">
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>58</v>
+        <v>195</v>
       </c>
       <c r="C57" s="4">
-        <v>760</v>
+        <v>160</v>
       </c>
       <c r="D57" s="2">
         <v>9</v>
@@ -2041,13 +2032,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="C58" s="4">
-        <v>160</v>
+        <v>657.5</v>
       </c>
       <c r="D58" s="2">
         <v>9</v>
@@ -2058,13 +2049,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="C59" s="4">
-        <v>657.5</v>
+        <v>135</v>
       </c>
       <c r="D59" s="2">
         <v>9</v>
@@ -2075,13 +2066,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="C60" s="4">
-        <v>135</v>
+        <v>577</v>
       </c>
       <c r="D60" s="2">
         <v>9</v>
@@ -2092,217 +2083,217 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61" s="4">
-        <v>577</v>
+        <v>1980</v>
       </c>
       <c r="D61" s="2">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" s="4">
-        <v>1980</v>
+        <v>100.04900000000001</v>
       </c>
       <c r="D62" s="2">
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C63" s="4">
-        <v>100.04900000000001</v>
+        <v>15.55</v>
       </c>
       <c r="D63" s="2">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C64" s="4">
-        <v>15.55</v>
+        <v>21.7</v>
       </c>
       <c r="D64" s="2">
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C65" s="4">
-        <v>21.7</v>
+        <v>2.5</v>
       </c>
       <c r="D65" s="2">
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C66" s="4">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="D66" s="2">
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C67" s="4">
-        <v>0.7</v>
+        <v>60.8</v>
       </c>
       <c r="D67" s="2">
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C68" s="4">
-        <v>60.8</v>
+        <v>185</v>
       </c>
       <c r="D68" s="2">
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="C69" s="4">
-        <v>370</v>
+        <v>31.83</v>
       </c>
       <c r="D69" s="2">
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C70" s="4">
-        <v>185</v>
+        <v>151.4</v>
       </c>
       <c r="D70" s="2">
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C71" s="4">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="D71" s="2">
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C72" s="4">
-        <v>31.83</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2">
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C73" s="4">
-        <v>151.4</v>
+        <v>54</v>
       </c>
       <c r="D73" s="2">
         <v>9</v>
@@ -2313,13 +2304,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C74" s="4">
-        <v>36</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="D74" s="2">
         <v>9</v>
@@ -2330,64 +2321,64 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C75" s="4">
-        <v>11</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="D75" s="2">
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C76" s="4">
-        <v>54</v>
+        <v>9.65</v>
       </c>
       <c r="D76" s="2">
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C77" s="4">
-        <v>19.600000000000001</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D77" s="2">
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>173</v>
+        <v>404</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C78" s="4">
-        <v>19.559999999999999</v>
+        <v>25</v>
       </c>
       <c r="D78" s="2">
         <v>9</v>
@@ -2398,333 +2389,333 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>174</v>
+        <v>785</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="C79" s="4">
-        <v>9.65</v>
+        <v>50</v>
       </c>
       <c r="D79" s="2">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>186</v>
+        <v>870</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C80" s="4">
-        <v>2.2000000000000002</v>
+        <v>13</v>
       </c>
       <c r="D80" s="2">
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>404</v>
+        <v>936</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C81" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D81" s="2">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>785</v>
+        <v>1494</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="C82" s="4">
-        <v>50</v>
+        <v>329.4</v>
       </c>
       <c r="D82" s="2">
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>870</v>
+        <v>1610</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C83" s="4">
-        <v>13</v>
+        <v>90.6</v>
       </c>
       <c r="D83" s="2">
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>936</v>
+        <v>1961</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C84" s="4">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D84" s="2">
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>1494</v>
+        <v>2215</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C85" s="4">
-        <v>329.4</v>
+        <v>24.658000000000001</v>
       </c>
       <c r="D85" s="2">
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>1610</v>
+        <v>2223</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C86" s="4">
-        <v>90.6</v>
+        <v>211</v>
       </c>
       <c r="D86" s="2">
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>1961</v>
+        <v>2572</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C87" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D87" s="2">
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>2215</v>
+        <v>2728</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C88" s="4">
-        <v>24.658000000000001</v>
+        <v>131.4</v>
       </c>
       <c r="D88" s="2">
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>2223</v>
+        <v>2794</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C89" s="4">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c r="D89" s="2">
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>2572</v>
+        <v>2833</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C90" s="4">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="D90" s="2">
         <v>9</v>
       </c>
       <c r="E90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>2728</v>
+        <v>3202</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C91" s="4">
-        <v>131.4</v>
+        <v>7.9</v>
       </c>
       <c r="D91" s="2">
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>2794</v>
+        <v>3203</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C92" s="4">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D92" s="2">
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>2833</v>
+        <v>3204</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C93" s="4">
-        <v>30.7</v>
+        <v>301</v>
       </c>
       <c r="D93" s="2">
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>3202</v>
+        <v>3220</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C94" s="4">
-        <v>7.9</v>
+        <v>21</v>
       </c>
       <c r="D94" s="2">
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>3203</v>
+        <v>3643</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C95" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D95" s="2">
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>3204</v>
+        <v>3932</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C96" s="4">
-        <v>301</v>
+        <v>35</v>
       </c>
       <c r="D96" s="2">
         <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>3220</v>
+        <v>3933</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C97" s="4">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D97" s="2">
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>3643</v>
+        <v>3935</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C98" s="4">
         <v>25</v>
@@ -2733,290 +2724,290 @@
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>3932</v>
+        <v>3936</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C99" s="4">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D99" s="2">
         <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>3933</v>
+        <v>3937</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C100" s="4">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D100" s="2">
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>3935</v>
+        <v>3962</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C101" s="4">
-        <v>25</v>
+        <v>135.82300000000001</v>
       </c>
       <c r="D101" s="2">
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>3936</v>
+        <v>4045</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C102" s="4">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="D102" s="2">
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>3937</v>
+        <v>4047</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C103" s="4">
-        <v>20</v>
+        <v>20.887</v>
       </c>
       <c r="D103" s="2">
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>3962</v>
+        <v>4106</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C104" s="4">
-        <v>135.82300000000001</v>
+        <v>25</v>
       </c>
       <c r="D104" s="2">
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>4045</v>
+        <v>4161</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C105" s="4">
-        <v>13.3</v>
+        <v>94</v>
       </c>
       <c r="D105" s="2">
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>4047</v>
+        <v>4256</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C106" s="4">
-        <v>20.887</v>
+        <v>40</v>
       </c>
       <c r="D106" s="2">
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>4106</v>
+        <v>4319</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C107" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D107" s="2">
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>4161</v>
+        <v>4329</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C108" s="4">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="D108" s="2">
         <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>4256</v>
+        <v>4377</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C109" s="4">
-        <v>40</v>
+        <v>29.5</v>
       </c>
       <c r="D109" s="2">
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>4319</v>
+        <v>4477</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C110" s="4">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="D110" s="2">
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>4329</v>
+        <v>4478</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C111" s="4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D111" s="2">
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>4377</v>
+        <v>4478</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C112" s="4">
-        <v>29.5</v>
+        <v>800</v>
       </c>
       <c r="D112" s="2">
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>4477</v>
+        <v>4478</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C113" s="4">
-        <v>18.8</v>
+        <v>2100</v>
       </c>
       <c r="D113" s="2">
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C114" s="4">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="D114" s="2">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>4478</v>
+        <v>4729</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C115" s="4">
-        <v>2100</v>
+        <v>318.8</v>
       </c>
       <c r="D115" s="2">
         <v>9</v>
@@ -3027,13 +3018,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>4479</v>
+        <v>4730</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C116" s="4">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D116" s="2">
         <v>9</v>
@@ -3044,61 +3035,61 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>4729</v>
+        <v>4799</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C117" s="4">
-        <v>318.8</v>
+        <v>218.01</v>
       </c>
       <c r="D117" s="2">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>4730</v>
+        <v>4848</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C118" s="4">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="D118" s="2">
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>4799</v>
+        <v>5022</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C119" s="4">
-        <v>218.01</v>
+        <v>25</v>
       </c>
       <c r="D119" s="2">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>4848</v>
+        <v>5087</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="C120" s="4">
         <v>25</v>
@@ -3107,100 +3098,100 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>5022</v>
+        <v>5117</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C121" s="4">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D121" s="2">
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>5087</v>
+        <v>5120</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C122" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D122" s="2">
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>5117</v>
+        <v>5187</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C123" s="4">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="D123" s="2">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>5120</v>
+        <v>5260</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="C124" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D124" s="2">
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>5187</v>
+        <v>5373</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C125" s="4">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="D125" s="2">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>5260</v>
+        <v>5736</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C126" s="4">
         <v>5</v>
@@ -3209,177 +3200,177 @@
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>5373</v>
+        <v>5741</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C127" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D127" s="2">
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>5736</v>
+        <v>5742</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C128" s="4">
-        <v>5</v>
+        <v>19.2</v>
       </c>
       <c r="D128" s="2">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>5741</v>
+        <v>5743</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C129" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D129" s="2">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>5742</v>
+        <v>5747</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C130" s="4">
-        <v>19.2</v>
+        <v>5.98</v>
       </c>
       <c r="D130" s="2">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>5743</v>
+        <v>5748</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C131" s="4">
-        <v>2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D131" s="2">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>5747</v>
+        <v>5750</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C132" s="4">
-        <v>5.98</v>
+        <v>28.7</v>
       </c>
       <c r="D132" s="2">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>5748</v>
+        <v>5796</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C133" s="4">
-        <v>4.5999999999999996</v>
+        <v>50</v>
       </c>
       <c r="D133" s="2">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>5750</v>
+        <v>5796</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>128</v>
       </c>
       <c r="C134" s="4">
-        <v>28.7</v>
+        <v>150</v>
       </c>
       <c r="D134" s="2">
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>129</v>
       </c>
       <c r="C135" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D135" s="2">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>129</v>
       </c>
       <c r="C136" s="4">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D136" s="2">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3387,118 +3378,118 @@
         <v>5797</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C137" s="4">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="D137" s="2">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>5797</v>
+        <v>5809</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C138" s="4">
-        <v>800</v>
+        <v>359.4</v>
       </c>
       <c r="D138" s="2">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C139" s="4">
-        <v>359.4</v>
+        <v>1260</v>
       </c>
       <c r="D139" s="2">
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C140" s="4">
-        <v>1260</v>
+        <v>160.30000000000001</v>
       </c>
       <c r="D140" s="2">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C141" s="4">
-        <v>160.30000000000001</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="D141" s="2">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>5812</v>
+        <v>5856</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C142" s="4">
-        <v>159.80000000000001</v>
+        <v>110</v>
       </c>
       <c r="D142" s="2">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>5856</v>
+        <v>6505</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>135</v>
       </c>
       <c r="C143" s="4">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D143" s="2">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -3506,33 +3497,33 @@
         <v>6505</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C144" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D144" s="2">
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C145" s="4">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D145" s="2">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -3540,16 +3531,16 @@
         <v>6506</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C146" s="4">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="D146" s="2">
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -3557,16 +3548,16 @@
         <v>6506</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C147" s="4">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="D147" s="2">
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -3574,7 +3565,7 @@
         <v>6507</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C148" s="4">
         <v>100</v>
@@ -3583,7 +3574,7 @@
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -3591,7 +3582,7 @@
         <v>6507</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C149" s="4">
         <v>400</v>
@@ -3600,7 +3591,7 @@
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -3608,7 +3599,7 @@
         <v>6508</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C150" s="4">
         <v>14.9</v>
@@ -3617,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -3625,7 +3616,7 @@
         <v>6508</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C151" s="4">
         <v>150</v>
@@ -3634,7 +3625,7 @@
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -3642,7 +3633,7 @@
         <v>6509</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C152" s="4">
         <v>82.8</v>
@@ -3651,7 +3642,7 @@
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -3659,7 +3650,7 @@
         <v>6510</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C153" s="4">
         <v>50</v>
@@ -3668,7 +3659,7 @@
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -3676,7 +3667,7 @@
         <v>6510</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C154" s="4">
         <v>100</v>
@@ -3685,7 +3676,7 @@
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -3693,7 +3684,7 @@
         <v>6511</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C155" s="4">
         <v>300</v>
@@ -3702,7 +3693,7 @@
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -3710,7 +3701,7 @@
         <v>6512</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C156" s="4">
         <v>24.998999999999999</v>
@@ -3719,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -3727,7 +3718,7 @@
         <v>6514</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C157" s="4">
         <v>100</v>
@@ -3736,7 +3727,7 @@
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -3744,7 +3735,7 @@
         <v>6514</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C158" s="4">
         <v>250</v>
@@ -3753,7 +3744,7 @@
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -3761,7 +3752,7 @@
         <v>6828</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C159" s="4">
         <v>150</v>
@@ -3770,7 +3761,7 @@
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -3778,10 +3769,10 @@
         <v>8329</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C160" s="4">
-        <v>4750</v>
+        <v>3800</v>
       </c>
       <c r="D160" s="2">
         <v>9</v>
@@ -3795,7 +3786,7 @@
         <v>8894</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C161" s="4">
         <v>540</v>
@@ -3804,7 +3795,7 @@
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -3812,7 +3803,7 @@
         <v>8895</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C162" s="4">
         <v>36.6</v>
@@ -3821,7 +3812,7 @@
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -3829,7 +3820,7 @@
         <v>8930</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C163" s="4">
         <v>25</v>
@@ -3838,7 +3829,7 @@
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -3846,7 +3837,7 @@
         <v>9716</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C164" s="4">
         <v>18</v>
@@ -3855,7 +3846,7 @@
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -3863,16 +3854,16 @@
         <v>9716</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C165" s="4">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D165" s="2">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -3880,16 +3871,16 @@
         <v>10497</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C166" s="4">
-        <v>1710</v>
+        <v>950</v>
       </c>
       <c r="D166" s="2">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -3897,7 +3888,7 @@
         <v>10907</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C167" s="4">
         <v>2</v>
@@ -3906,7 +3897,7 @@
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -3914,7 +3905,7 @@
         <v>11259</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C168" s="4">
         <v>25</v>
@@ -3923,7 +3914,7 @@
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -3931,7 +3922,7 @@
         <v>11370</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C169" s="4">
         <v>180</v>
@@ -3940,7 +3931,7 @@
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -3948,16 +3939,16 @@
         <v>11370</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C170" s="4">
-        <v>2700</v>
+        <v>2340</v>
       </c>
       <c r="D170" s="2">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -3965,16 +3956,16 @@
         <v>11370</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C171" s="4">
-        <v>3060</v>
+        <v>2700</v>
       </c>
       <c r="D171" s="2">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -3982,7 +3973,7 @@
         <v>11371</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C172" s="4">
         <v>897</v>
@@ -3991,7 +3982,7 @@
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
@@ -3999,7 +3990,7 @@
         <v>11372</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C173" s="4">
         <v>540</v>
@@ -4008,7 +3999,7 @@
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
@@ -4016,7 +4007,7 @@
         <v>11373</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C174" s="4">
         <v>705</v>
@@ -4025,7 +4016,7 @@
         <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
@@ -4033,16 +4024,16 @@
         <v>11374</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C175" s="4">
-        <v>1980</v>
+        <v>1800</v>
       </c>
       <c r="D175" s="2">
         <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
@@ -4050,7 +4041,7 @@
         <v>11377</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C176" s="4">
         <v>300</v>
@@ -4059,7 +4050,7 @@
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
@@ -4067,7 +4058,7 @@
         <v>11377</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C177" s="4">
         <v>2700</v>
@@ -4076,7 +4067,7 @@
         <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
@@ -4084,7 +4075,7 @@
         <v>11378</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C178" s="4">
         <v>180</v>
@@ -4093,7 +4084,7 @@
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
@@ -4101,16 +4092,16 @@
         <v>11379</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C179" s="4">
-        <v>1440</v>
+        <v>1260</v>
       </c>
       <c r="D179" s="2">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -4118,7 +4109,7 @@
         <v>11380</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C180" s="4">
         <v>180</v>
@@ -4127,7 +4118,7 @@
         <v>9</v>
       </c>
       <c r="E180" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
@@ -4135,7 +4126,7 @@
         <v>11612</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C181" s="4">
         <v>25</v>
@@ -4144,7 +4135,7 @@
         <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
@@ -4152,7 +4143,7 @@
         <v>11849</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C182" s="4">
         <v>50</v>
@@ -4161,7 +4152,7 @@
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
@@ -4169,7 +4160,7 @@
         <v>12710</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C183" s="4">
         <v>2.5</v>
@@ -4178,7 +4169,7 @@
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
@@ -4186,7 +4177,7 @@
         <v>12711</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C184" s="4">
         <v>1</v>
@@ -4195,7 +4186,7 @@
         <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
@@ -4203,7 +4194,7 @@
         <v>12712</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C185" s="4">
         <v>0.06</v>
@@ -4212,7 +4203,7 @@
         <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
@@ -4220,7 +4211,7 @@
         <v>12713</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C186" s="4">
         <v>1</v>
@@ -4229,7 +4220,7 @@
         <v>9</v>
       </c>
       <c r="E186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
@@ -4237,7 +4228,7 @@
         <v>12714</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C187" s="4">
         <v>0.05</v>
@@ -4246,7 +4237,7 @@
         <v>9</v>
       </c>
       <c r="E187" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
@@ -4254,7 +4245,7 @@
         <v>12715</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C188" s="4">
         <v>0.05</v>
@@ -4263,7 +4254,7 @@
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
@@ -4271,7 +4262,7 @@
         <v>12716</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C189" s="4">
         <v>0.05</v>
@@ -4280,7 +4271,7 @@
         <v>9</v>
       </c>
       <c r="E189" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
@@ -4288,7 +4279,7 @@
         <v>12717</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C190" s="4">
         <v>0.05</v>
@@ -4297,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
@@ -4305,7 +4296,7 @@
         <v>12718</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C191" s="4">
         <v>1</v>
@@ -4314,7 +4305,7 @@
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
@@ -4322,7 +4313,7 @@
         <v>12924</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C192" s="4">
         <v>20</v>
@@ -4331,7 +4322,7 @@
         <v>9</v>
       </c>
       <c r="E192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
@@ -4339,7 +4330,7 @@
         <v>14753</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C193" s="4">
         <v>711</v>
@@ -4348,29 +4339,29 @@
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>14925</v>
+        <v>15176</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="C194" s="4">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="D194" s="2">
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>15176</v>
+        <v>15178</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>175</v>
@@ -4382,46 +4373,46 @@
         <v>9</v>
       </c>
       <c r="E195" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>15178</v>
+        <v>15180</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>176</v>
       </c>
       <c r="C196" s="4">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D196" s="2">
         <v>9</v>
       </c>
       <c r="E196" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>15180</v>
+        <v>15181</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C197" s="4">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D197" s="2">
         <v>9</v>
       </c>
       <c r="E197" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>15181</v>
+        <v>15182</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>178</v>
@@ -4433,75 +4424,75 @@
         <v>9</v>
       </c>
       <c r="E198" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>15182</v>
+        <v>15183</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C199" s="4">
-        <v>210</v>
+        <v>1540</v>
       </c>
       <c r="D199" s="2">
         <v>9</v>
       </c>
       <c r="E199" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>15183</v>
+        <v>15184</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C200" s="4">
-        <v>1540</v>
+        <v>200</v>
       </c>
       <c r="D200" s="2">
         <v>9</v>
       </c>
       <c r="E200" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>15184</v>
+        <v>15185</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C201" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D201" s="2">
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>15185</v>
+        <v>15187</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C202" s="4">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="D202" s="2">
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
@@ -4509,33 +4500,33 @@
         <v>15187</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C203" s="4">
-        <v>41.5</v>
+        <v>125</v>
       </c>
       <c r="D203" s="2">
         <v>9</v>
       </c>
       <c r="E203" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
-        <v>15187</v>
+        <v>16336</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C204" s="4">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D204" s="2">
         <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -4543,33 +4534,33 @@
         <v>16336</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C205" s="4">
-        <v>180</v>
+        <v>3060</v>
       </c>
       <c r="D205" s="2">
         <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
-        <v>16336</v>
+        <v>16684</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>184</v>
       </c>
       <c r="C206" s="4">
-        <v>3240</v>
+        <v>360</v>
       </c>
       <c r="D206" s="2">
         <v>9</v>
       </c>
       <c r="E206" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
@@ -4577,33 +4568,33 @@
         <v>16684</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C207" s="4">
-        <v>360</v>
+        <v>2340</v>
       </c>
       <c r="D207" s="2">
         <v>9</v>
       </c>
       <c r="E207" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
-        <v>16684</v>
+        <v>17930</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C208" s="4">
-        <v>2340</v>
+        <v>680</v>
       </c>
       <c r="D208" s="2">
         <v>9</v>
       </c>
       <c r="E208" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">

--- a/data-source/ESTOQUEQUIMICOS.xlsx
+++ b/data-source/ESTOQUEQUIMICOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3DD17542-BBA7-45E6-A128-B4D037E0B204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B1EAA45-9E5E-4795-87B8-F70C107CD20B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB56254C-E439-4A0B-9987-A1FDEE370BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="202">
   <si>
     <t>Produto</t>
   </si>
@@ -1051,7 +1051,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -2939,7 +2939,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="4">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="D111" s="2">
         <v>9</v>
@@ -2956,7 +2956,7 @@
         <v>110</v>
       </c>
       <c r="C112" s="4">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="D112" s="2">
         <v>9</v>
@@ -2967,13 +2967,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C113" s="4">
-        <v>2100</v>
+        <v>150</v>
       </c>
       <c r="D113" s="2">
         <v>9</v>
@@ -2984,30 +2984,30 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>4479</v>
+        <v>4729</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C114" s="4">
-        <v>150</v>
+        <v>318.8</v>
       </c>
       <c r="D114" s="2">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>4729</v>
+        <v>4730</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C115" s="4">
-        <v>318.8</v>
+        <v>144</v>
       </c>
       <c r="D115" s="2">
         <v>9</v>
@@ -3018,13 +3018,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>4730</v>
+        <v>4799</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C116" s="4">
-        <v>144</v>
+        <v>218.01</v>
       </c>
       <c r="D116" s="2">
         <v>9</v>
@@ -3035,27 +3035,27 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>4799</v>
+        <v>4848</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C117" s="4">
-        <v>218.01</v>
+        <v>25</v>
       </c>
       <c r="D117" s="2">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>4848</v>
+        <v>5022</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C118" s="4">
         <v>25</v>
@@ -3064,15 +3064,15 @@
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>5022</v>
+        <v>5087</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="C119" s="4">
         <v>25</v>
@@ -3086,98 +3086,98 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>5087</v>
+        <v>5117</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="C120" s="4">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D120" s="2">
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>5117</v>
+        <v>5120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="C121" s="4">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D121" s="2">
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>5120</v>
+        <v>5187</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="C122" s="4">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="D122" s="2">
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>5187</v>
+        <v>5260</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C123" s="4">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="D123" s="2">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>5260</v>
+        <v>5373</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C124" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D124" s="2">
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>5373</v>
+        <v>5736</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C125" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D125" s="2">
         <v>9</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>5736</v>
+        <v>5741</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C126" s="4">
         <v>5</v>
@@ -3200,35 +3200,35 @@
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>185</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C127" s="4">
-        <v>5</v>
+        <v>19.2</v>
       </c>
       <c r="D127" s="2">
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C128" s="4">
-        <v>19.2</v>
+        <v>2</v>
       </c>
       <c r="D128" s="2">
         <v>9</v>
@@ -3239,70 +3239,70 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>5743</v>
+        <v>5747</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C129" s="4">
-        <v>2</v>
+        <v>5.98</v>
       </c>
       <c r="D129" s="2">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C130" s="4">
-        <v>5.98</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D130" s="2">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>5748</v>
+        <v>5750</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C131" s="4">
-        <v>4.5999999999999996</v>
+        <v>28.7</v>
       </c>
       <c r="D131" s="2">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>5750</v>
+        <v>5796</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C132" s="4">
-        <v>28.7</v>
+        <v>50</v>
       </c>
       <c r="D132" s="2">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3313,7 +3313,7 @@
         <v>128</v>
       </c>
       <c r="C133" s="4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D133" s="2">
         <v>9</v>
@@ -3324,13 +3324,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C134" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D134" s="2">
         <v>9</v>
@@ -3347,7 +3347,7 @@
         <v>129</v>
       </c>
       <c r="C135" s="4">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="D135" s="2">
         <v>9</v>
@@ -3358,47 +3358,47 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>5797</v>
+        <v>5809</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C136" s="4">
-        <v>300</v>
+        <v>359.4</v>
       </c>
       <c r="D136" s="2">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>5797</v>
+        <v>5810</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C137" s="4">
-        <v>900</v>
+        <v>1260</v>
       </c>
       <c r="D137" s="2">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>5809</v>
+        <v>5811</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C138" s="4">
-        <v>359.4</v>
+        <v>160.30000000000001</v>
       </c>
       <c r="D138" s="2">
         <v>9</v>
@@ -3409,13 +3409,13 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>5810</v>
+        <v>5812</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C139" s="4">
-        <v>1260</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="D139" s="2">
         <v>9</v>
@@ -3426,64 +3426,64 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>5811</v>
+        <v>5856</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C140" s="4">
-        <v>160.30000000000001</v>
+        <v>110</v>
       </c>
       <c r="D140" s="2">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>5812</v>
+        <v>6505</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C141" s="4">
-        <v>159.80000000000001</v>
+        <v>50</v>
       </c>
       <c r="D141" s="2">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>5856</v>
+        <v>6505</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C142" s="4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D142" s="2">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C143" s="4">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="D143" s="2">
         <v>9</v>
@@ -3494,13 +3494,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C144" s="4">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="D144" s="2">
         <v>9</v>
@@ -3511,13 +3511,13 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>6506</v>
+        <v>6507</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C145" s="4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D145" s="2">
         <v>9</v>
@@ -3528,13 +3528,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>6506</v>
+        <v>6507</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C146" s="4">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="D146" s="2">
         <v>9</v>
@@ -3545,13 +3545,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>6506</v>
+        <v>6508</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C147" s="4">
-        <v>650</v>
+        <v>14.9</v>
       </c>
       <c r="D147" s="2">
         <v>9</v>
@@ -3562,13 +3562,13 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>6507</v>
+        <v>6508</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C148" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D148" s="2">
         <v>9</v>
@@ -3579,13 +3579,13 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>6507</v>
+        <v>6509</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C149" s="4">
-        <v>400</v>
+        <v>82.8</v>
       </c>
       <c r="D149" s="2">
         <v>9</v>
@@ -3596,13 +3596,13 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>6508</v>
+        <v>6510</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C150" s="4">
-        <v>14.9</v>
+        <v>50</v>
       </c>
       <c r="D150" s="2">
         <v>9</v>
@@ -3613,13 +3613,13 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>6508</v>
+        <v>6510</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C151" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D151" s="2">
         <v>9</v>
@@ -3630,13 +3630,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>6509</v>
+        <v>6511</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C152" s="4">
-        <v>82.8</v>
+        <v>300</v>
       </c>
       <c r="D152" s="2">
         <v>9</v>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>6510</v>
+        <v>6512</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C153" s="4">
-        <v>50</v>
+        <v>24.998999999999999</v>
       </c>
       <c r="D153" s="2">
         <v>9</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>6510</v>
+        <v>6514</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C154" s="4">
         <v>100</v>
@@ -3681,13 +3681,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>6511</v>
+        <v>6514</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C155" s="4">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D155" s="2">
         <v>9</v>
@@ -3698,64 +3698,64 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>6512</v>
+        <v>6828</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C156" s="4">
-        <v>24.998999999999999</v>
+        <v>150</v>
       </c>
       <c r="D156" s="2">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>6514</v>
+        <v>8329</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C157" s="4">
-        <v>100</v>
+        <v>3800</v>
       </c>
       <c r="D157" s="2">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>6514</v>
+        <v>8894</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C158" s="4">
-        <v>250</v>
+        <v>540</v>
       </c>
       <c r="D158" s="2">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>6828</v>
+        <v>8895</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C159" s="4">
-        <v>150</v>
+        <v>36.6</v>
       </c>
       <c r="D159" s="2">
         <v>9</v>
@@ -3766,166 +3766,166 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>8329</v>
+        <v>8930</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C160" s="4">
-        <v>3800</v>
+        <v>25</v>
       </c>
       <c r="D160" s="2">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>8894</v>
+        <v>9716</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C161" s="4">
-        <v>540</v>
+        <v>18</v>
       </c>
       <c r="D161" s="2">
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>8895</v>
+        <v>9716</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C162" s="4">
-        <v>36.6</v>
+        <v>18</v>
       </c>
       <c r="D162" s="2">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>8930</v>
+        <v>10497</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C163" s="4">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="D163" s="2">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>9716</v>
+        <v>10907</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C164" s="4">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D164" s="2">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>9716</v>
+        <v>11259</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C165" s="4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D165" s="2">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>10497</v>
+        <v>11370</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C166" s="4">
-        <v>950</v>
+        <v>180</v>
       </c>
       <c r="D166" s="2">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>10907</v>
+        <v>11370</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C167" s="4">
-        <v>2</v>
+        <v>2340</v>
       </c>
       <c r="D167" s="2">
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>11259</v>
+        <v>11370</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C168" s="4">
-        <v>25</v>
+        <v>2700</v>
       </c>
       <c r="D168" s="2">
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>11370</v>
+        <v>11371</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C169" s="4">
-        <v>180</v>
+        <v>897</v>
       </c>
       <c r="D169" s="2">
         <v>9</v>
@@ -3936,13 +3936,13 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>11370</v>
+        <v>11372</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C170" s="4">
-        <v>2340</v>
+        <v>540</v>
       </c>
       <c r="D170" s="2">
         <v>9</v>
@@ -3953,13 +3953,13 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>11370</v>
+        <v>11373</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C171" s="4">
-        <v>2700</v>
+        <v>705</v>
       </c>
       <c r="D171" s="2">
         <v>9</v>
@@ -3970,13 +3970,13 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>11371</v>
+        <v>11374</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="C172" s="4">
-        <v>897</v>
+        <v>1800</v>
       </c>
       <c r="D172" s="2">
         <v>9</v>
@@ -3987,13 +3987,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>11372</v>
+        <v>11377</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C173" s="4">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="D173" s="2">
         <v>9</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>11373</v>
+        <v>11377</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C174" s="4">
-        <v>705</v>
+        <v>2700</v>
       </c>
       <c r="D174" s="2">
         <v>9</v>
@@ -4021,13 +4021,13 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>11374</v>
+        <v>11378</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="C175" s="4">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="D175" s="2">
         <v>9</v>
@@ -4038,13 +4038,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>11377</v>
+        <v>11379</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C176" s="4">
-        <v>300</v>
+        <v>1260</v>
       </c>
       <c r="D176" s="2">
         <v>9</v>
@@ -4055,13 +4055,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>11377</v>
+        <v>11380</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C177" s="4">
-        <v>2700</v>
+        <v>180</v>
       </c>
       <c r="D177" s="2">
         <v>9</v>
@@ -4072,47 +4072,47 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>11378</v>
+        <v>11612</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C178" s="4">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="D178" s="2">
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>11379</v>
+        <v>11849</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C179" s="4">
-        <v>1260</v>
+        <v>50</v>
       </c>
       <c r="D179" s="2">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>11380</v>
+        <v>12710</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C180" s="4">
-        <v>180</v>
+        <v>2.5</v>
       </c>
       <c r="D180" s="2">
         <v>9</v>
@@ -4123,47 +4123,47 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>11612</v>
+        <v>12711</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C181" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2">
         <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>11849</v>
+        <v>12712</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C182" s="4">
-        <v>50</v>
+        <v>0.06</v>
       </c>
       <c r="D182" s="2">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C183" s="4">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D183" s="2">
         <v>9</v>
@@ -4174,30 +4174,30 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>12711</v>
+        <v>12714</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C184" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D184" s="2">
         <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>12712</v>
+        <v>12715</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C185" s="4">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D185" s="2">
         <v>9</v>
@@ -4208,13 +4208,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>12713</v>
+        <v>12716</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C186" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D186" s="2">
         <v>9</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>12714</v>
+        <v>12717</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C187" s="4">
         <v>0.05</v>
@@ -4237,18 +4237,18 @@
         <v>9</v>
       </c>
       <c r="E187" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>12715</v>
+        <v>12718</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C188" s="4">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="D188" s="2">
         <v>9</v>
@@ -4259,98 +4259,98 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>12716</v>
+        <v>12924</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C189" s="4">
-        <v>0.05</v>
+        <v>20</v>
       </c>
       <c r="D189" s="2">
         <v>9</v>
       </c>
       <c r="E189" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>12717</v>
+        <v>14753</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C190" s="4">
-        <v>0.05</v>
+        <v>711</v>
       </c>
       <c r="D190" s="2">
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>12718</v>
+        <v>15176</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C191" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="D191" s="2">
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>12924</v>
+        <v>15178</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C192" s="4">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="D192" s="2">
         <v>9</v>
       </c>
       <c r="E192" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>14753</v>
+        <v>15180</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C193" s="4">
-        <v>711</v>
+        <v>250</v>
       </c>
       <c r="D193" s="2">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>15176</v>
+        <v>15181</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C194" s="4">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="D194" s="2">
         <v>9</v>
@@ -4361,13 +4361,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>15178</v>
+        <v>15182</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C195" s="4">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="D195" s="2">
         <v>9</v>
@@ -4378,13 +4378,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>15180</v>
+        <v>15183</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C196" s="4">
-        <v>250</v>
+        <v>1540</v>
       </c>
       <c r="D196" s="2">
         <v>9</v>
@@ -4395,13 +4395,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>15181</v>
+        <v>15184</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C197" s="4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D197" s="2">
         <v>9</v>
@@ -4412,13 +4412,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>15182</v>
+        <v>15185</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C198" s="4">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="D198" s="2">
         <v>9</v>
@@ -4429,13 +4429,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>15183</v>
+        <v>15187</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C199" s="4">
-        <v>1540</v>
+        <v>41.5</v>
       </c>
       <c r="D199" s="2">
         <v>9</v>
@@ -4446,13 +4446,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>15184</v>
+        <v>15187</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C200" s="4">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="D200" s="2">
         <v>9</v>
@@ -4463,64 +4463,64 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>15185</v>
+        <v>16336</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C201" s="4">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="D201" s="2">
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>15187</v>
+        <v>16336</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C202" s="4">
-        <v>41.5</v>
+        <v>3060</v>
       </c>
       <c r="D202" s="2">
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
-        <v>15187</v>
+        <v>16684</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C203" s="4">
-        <v>125</v>
+        <v>360</v>
       </c>
       <c r="D203" s="2">
         <v>9</v>
       </c>
       <c r="E203" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
-        <v>16336</v>
+        <v>16684</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C204" s="4">
-        <v>180</v>
+        <v>2340</v>
       </c>
       <c r="D204" s="2">
         <v>9</v>
@@ -4531,77 +4531,26 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
-        <v>16336</v>
+        <v>17930</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C205" s="4">
-        <v>3060</v>
+        <v>680</v>
       </c>
       <c r="D205" s="2">
         <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C206" s="4">
-        <v>360</v>
-      </c>
-      <c r="D206" s="2">
-        <v>9</v>
-      </c>
-      <c r="E206" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C207" s="4">
-        <v>2340</v>
-      </c>
-      <c r="D207" s="2">
-        <v>9</v>
-      </c>
-      <c r="E207" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="2">
-        <v>17930</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C208" s="4">
-        <v>680</v>
-      </c>
-      <c r="D208" s="2">
-        <v>9</v>
-      </c>
-      <c r="E208" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="2"/>
-      <c r="B209" s="3"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="3"/>
+      <c r="A206" s="2"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="4"/>
+      <c r="D206" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data-source/ESTOQUEQUIMICOS.xlsx
+++ b/data-source/ESTOQUEQUIMICOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB56254C-E439-4A0B-9987-A1FDEE370BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB227DAF-32AB-4B7A-AEFE-06283F791D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="205">
   <si>
     <t>Produto</t>
   </si>
@@ -643,6 +643,15 @@
   </si>
   <si>
     <t>RESINA LARITHANE AL 233</t>
+  </si>
+  <si>
+    <t>RESINA STAHL 16106</t>
+  </si>
+  <si>
+    <t>RESINA STAHL 4715</t>
+  </si>
+  <si>
+    <t>RESINA STAHL 10088</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1060,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1097,64 +1106,64 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="C3" s="4">
-        <v>172.5</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4">
-        <v>130</v>
+        <v>172.5</v>
       </c>
       <c r="D4" s="2">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="D5" s="2">
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>194</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2">
         <v>9</v>
@@ -1165,30 +1174,30 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="C7" s="4">
-        <v>13.3</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4">
-        <v>180</v>
+        <v>13.3</v>
       </c>
       <c r="D8" s="2">
         <v>9</v>
@@ -1199,13 +1208,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4">
-        <v>470</v>
+        <v>180</v>
       </c>
       <c r="D9" s="2">
         <v>9</v>
@@ -1216,13 +1225,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="D10" s="2">
         <v>9</v>
@@ -1233,30 +1242,30 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="4">
-        <v>1833.8610000000001</v>
+        <v>410</v>
       </c>
       <c r="D11" s="2">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>372</v>
+        <v>1800</v>
       </c>
       <c r="D12" s="2">
         <v>9</v>
@@ -1267,98 +1276,98 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="4">
-        <v>25</v>
+        <v>372</v>
       </c>
       <c r="D13" s="2">
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="4">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4">
-        <v>1.4</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2">
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="4">
-        <v>0.89</v>
+        <v>1.4</v>
       </c>
       <c r="D16" s="2">
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4">
-        <v>101.7</v>
+        <v>0.89</v>
       </c>
       <c r="D17" s="2">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="4">
-        <v>95</v>
+        <v>101.7</v>
       </c>
       <c r="D18" s="2">
         <v>9</v>
@@ -1369,30 +1378,30 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
-        <v>2.85</v>
+        <v>95</v>
       </c>
       <c r="D19" s="2">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
-        <v>0.65</v>
+        <v>2.85</v>
       </c>
       <c r="D20" s="2">
         <v>9</v>
@@ -1403,13 +1412,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
-        <v>2.6</v>
+        <v>0.65</v>
       </c>
       <c r="D21" s="2">
         <v>9</v>
@@ -1420,47 +1429,47 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="D22" s="2">
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4">
-        <v>4.8899999999999997</v>
+        <v>7.6</v>
       </c>
       <c r="D23" s="2">
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="4">
-        <v>5</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="D24" s="2">
         <v>9</v>
@@ -1471,10 +1480,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="4">
         <v>5</v>
@@ -1488,10 +1497,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4">
         <v>5</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4">
         <v>5</v>
@@ -1522,10 +1531,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4">
         <v>5</v>
@@ -1539,98 +1548,98 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2">
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="4">
-        <v>4.96</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2">
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" s="4">
-        <v>9</v>
+        <v>4.96</v>
       </c>
       <c r="D31" s="2">
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="4">
-        <v>106.64</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2">
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="4">
-        <v>183.9</v>
+        <v>106.64</v>
       </c>
       <c r="D33" s="2">
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="4">
-        <v>375</v>
+        <v>183.9</v>
       </c>
       <c r="D34" s="2">
         <v>9</v>
@@ -1641,13 +1650,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="4">
-        <v>44</v>
+        <v>375</v>
       </c>
       <c r="D35" s="2">
         <v>9</v>
@@ -1658,13 +1667,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36" s="4">
-        <v>2.23</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2">
         <v>9</v>
@@ -1675,47 +1684,47 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="4">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="D37" s="2">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="4">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" s="4">
-        <v>19.5</v>
+        <v>5.9</v>
       </c>
       <c r="D39" s="2">
         <v>9</v>
@@ -1726,13 +1735,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="4">
-        <v>12.1</v>
+        <v>19.5</v>
       </c>
       <c r="D40" s="2">
         <v>9</v>
@@ -1743,13 +1752,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="4">
-        <v>13</v>
+        <v>12.1</v>
       </c>
       <c r="D41" s="2">
         <v>9</v>
@@ -1760,13 +1769,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42" s="4">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D42" s="2">
         <v>9</v>
@@ -1777,13 +1786,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="4">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="D43" s="2">
         <v>9</v>
@@ -1794,13 +1803,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D44" s="2">
         <v>9</v>
@@ -1811,13 +1820,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="4">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="D45" s="2">
         <v>9</v>
@@ -1828,13 +1837,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D46" s="2">
         <v>9</v>
@@ -1845,13 +1854,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D47" s="2">
         <v>9</v>
@@ -1862,13 +1871,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="4">
         <v>50</v>
-      </c>
-      <c r="C48" s="4">
-        <v>40</v>
       </c>
       <c r="D48" s="2">
         <v>9</v>
@@ -1879,64 +1888,64 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49" s="4">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D49" s="2">
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50" s="4">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D50" s="2">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="4">
-        <v>13.8</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2">
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" s="4">
-        <v>170</v>
+        <v>13.8</v>
       </c>
       <c r="D52" s="2">
         <v>9</v>
@@ -1947,13 +1956,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53" s="4">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="D53" s="2">
         <v>9</v>
@@ -1964,13 +1973,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C54" s="4">
-        <v>127.8</v>
+        <v>25</v>
       </c>
       <c r="D54" s="2">
         <v>9</v>
@@ -1981,13 +1990,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C55" s="4">
-        <v>17.899999999999999</v>
+        <v>127.8</v>
       </c>
       <c r="D55" s="2">
         <v>9</v>
@@ -1998,30 +2007,30 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C56" s="4">
-        <v>380</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D56" s="2">
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>195</v>
+        <v>58</v>
       </c>
       <c r="C57" s="4">
-        <v>160</v>
+        <v>1140</v>
       </c>
       <c r="D57" s="2">
         <v>9</v>
@@ -2032,13 +2041,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="C58" s="4">
-        <v>657.5</v>
+        <v>160</v>
       </c>
       <c r="D58" s="2">
         <v>9</v>
@@ -2049,13 +2058,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="C59" s="4">
-        <v>135</v>
+        <v>657.5</v>
       </c>
       <c r="D59" s="2">
         <v>9</v>
@@ -2066,13 +2075,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="C60" s="4">
-        <v>577</v>
+        <v>108</v>
       </c>
       <c r="D60" s="2">
         <v>9</v>
@@ -2083,30 +2092,30 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C61" s="4">
-        <v>1980</v>
+        <v>577</v>
       </c>
       <c r="D61" s="2">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>185</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="4">
-        <v>100.04900000000001</v>
+        <v>1980</v>
       </c>
       <c r="D62" s="2">
         <v>9</v>
@@ -2117,13 +2126,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" s="4">
-        <v>15.55</v>
+        <v>100.04900000000001</v>
       </c>
       <c r="D63" s="2">
         <v>9</v>
@@ -2134,47 +2143,47 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" s="4">
-        <v>21.7</v>
+        <v>15.55</v>
       </c>
       <c r="D64" s="2">
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C65" s="4">
-        <v>2.5</v>
+        <v>21.7</v>
       </c>
       <c r="D65" s="2">
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>193</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" s="4">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="D66" s="2">
         <v>9</v>
@@ -2185,30 +2194,30 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" s="4">
-        <v>60.8</v>
+        <v>0.7</v>
       </c>
       <c r="D67" s="2">
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" s="4">
-        <v>185</v>
+        <v>60.8</v>
       </c>
       <c r="D68" s="2">
         <v>9</v>
@@ -2219,13 +2228,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="C69" s="4">
-        <v>31.83</v>
+        <v>370</v>
       </c>
       <c r="D69" s="2">
         <v>9</v>
@@ -2236,13 +2245,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C70" s="4">
-        <v>151.4</v>
+        <v>185</v>
       </c>
       <c r="D70" s="2">
         <v>9</v>
@@ -2253,13 +2262,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="C71" s="4">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="D71" s="2">
         <v>9</v>
@@ -2270,13 +2279,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C72" s="4">
-        <v>11</v>
+        <v>31.83</v>
       </c>
       <c r="D72" s="2">
         <v>9</v>
@@ -2287,47 +2296,47 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C73" s="4">
-        <v>54</v>
+        <v>151.4</v>
       </c>
       <c r="D73" s="2">
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C74" s="4">
-        <v>19.600000000000001</v>
+        <v>36</v>
       </c>
       <c r="D74" s="2">
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C75" s="4">
-        <v>19.559999999999999</v>
+        <v>11</v>
       </c>
       <c r="D75" s="2">
         <v>9</v>
@@ -2338,132 +2347,132 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C76" s="4">
-        <v>9.65</v>
+        <v>54</v>
       </c>
       <c r="D76" s="2">
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
+        <v>169</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="4">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D77" s="2">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
         <v>186</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C77" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D77" s="2">
-        <v>9</v>
-      </c>
-      <c r="E77" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>404</v>
+        <v>173</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C78" s="4">
-        <v>25</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="D78" s="2">
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>785</v>
+        <v>174</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="C79" s="4">
-        <v>50</v>
+        <v>9.65</v>
       </c>
       <c r="D79" s="2">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>870</v>
+        <v>186</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C80" s="4">
-        <v>13</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D80" s="2">
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>936</v>
+        <v>404</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C81" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D81" s="2">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>1494</v>
+        <v>785</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="C82" s="4">
-        <v>329.4</v>
+        <v>50</v>
       </c>
       <c r="D82" s="2">
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>1610</v>
+        <v>870</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C83" s="4">
-        <v>90.6</v>
+        <v>13</v>
       </c>
       <c r="D83" s="2">
         <v>9</v>
@@ -2474,81 +2483,81 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>1961</v>
+        <v>936</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C84" s="4">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D84" s="2">
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>2215</v>
+        <v>1494</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C85" s="4">
-        <v>24.658000000000001</v>
+        <v>329.4</v>
       </c>
       <c r="D85" s="2">
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>2223</v>
+        <v>1610</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C86" s="4">
-        <v>211</v>
+        <v>90.6</v>
       </c>
       <c r="D86" s="2">
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>2572</v>
+        <v>1961</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C87" s="4">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D87" s="2">
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>193</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>2728</v>
+        <v>2215</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C88" s="4">
-        <v>131.4</v>
+        <v>24.658000000000001</v>
       </c>
       <c r="D88" s="2">
         <v>9</v>
@@ -2559,30 +2568,30 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>2794</v>
+        <v>2223</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C89" s="4">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="D89" s="2">
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>2833</v>
+        <v>2572</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C90" s="4">
-        <v>30.7</v>
+        <v>25</v>
       </c>
       <c r="D90" s="2">
         <v>9</v>
@@ -2593,129 +2602,129 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>3202</v>
+        <v>2728</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C91" s="4">
-        <v>7.9</v>
+        <v>131.4</v>
       </c>
       <c r="D91" s="2">
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>3203</v>
+        <v>2794</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C92" s="4">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D92" s="2">
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>3204</v>
+        <v>2833</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C93" s="4">
-        <v>301</v>
+        <v>30.7</v>
       </c>
       <c r="D93" s="2">
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>3220</v>
+        <v>3202</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C94" s="4">
-        <v>21</v>
+        <v>7.9</v>
       </c>
       <c r="D94" s="2">
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>3643</v>
+        <v>3203</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C95" s="4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D95" s="2">
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>3932</v>
+        <v>3204</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C96" s="4">
-        <v>35</v>
+        <v>301</v>
       </c>
       <c r="D96" s="2">
         <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>3933</v>
+        <v>3220</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C97" s="4">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D97" s="2">
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>3935</v>
+        <v>3643</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C98" s="4">
         <v>25</v>
@@ -2724,18 +2733,18 @@
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>3936</v>
+        <v>3932</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C99" s="4">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D99" s="2">
         <v>9</v>
@@ -2746,13 +2755,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>3937</v>
+        <v>3933</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C100" s="4">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D100" s="2">
         <v>9</v>
@@ -2763,30 +2772,30 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>3962</v>
+        <v>3935</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C101" s="4">
-        <v>135.82300000000001</v>
+        <v>25</v>
       </c>
       <c r="D101" s="2">
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>4045</v>
+        <v>3936</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C102" s="4">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="D102" s="2">
         <v>9</v>
@@ -2797,268 +2806,268 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>4047</v>
+        <v>3937</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C103" s="4">
-        <v>20.887</v>
+        <v>20</v>
       </c>
       <c r="D103" s="2">
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>4106</v>
+        <v>3962</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C104" s="4">
-        <v>25</v>
+        <v>135.82300000000001</v>
       </c>
       <c r="D104" s="2">
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>193</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>4161</v>
+        <v>4045</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C105" s="4">
-        <v>94</v>
+        <v>13.3</v>
       </c>
       <c r="D105" s="2">
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>4256</v>
+        <v>4047</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C106" s="4">
-        <v>40</v>
+        <v>20.887</v>
       </c>
       <c r="D106" s="2">
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>4319</v>
+        <v>4106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C107" s="4">
-        <v>30</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="D107" s="2">
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>4329</v>
+        <v>4161</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C108" s="4">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D108" s="2">
         <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>4377</v>
+        <v>4256</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C109" s="4">
-        <v>29.5</v>
+        <v>40</v>
       </c>
       <c r="D109" s="2">
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>4477</v>
+        <v>4319</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C110" s="4">
-        <v>18.8</v>
+        <v>30</v>
       </c>
       <c r="D110" s="2">
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>4478</v>
+        <v>4329</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C111" s="4">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="D111" s="2">
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>4478</v>
+        <v>4377</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C112" s="4">
-        <v>1600</v>
+        <v>29.5</v>
       </c>
       <c r="D112" s="2">
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>4479</v>
+        <v>4477</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C113" s="4">
-        <v>150</v>
+        <v>18.8</v>
       </c>
       <c r="D113" s="2">
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>4729</v>
+        <v>4478</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C114" s="4">
-        <v>318.8</v>
+        <v>100</v>
       </c>
       <c r="D114" s="2">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>4730</v>
+        <v>4478</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C115" s="4">
-        <v>144</v>
+        <v>800</v>
       </c>
       <c r="D115" s="2">
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>4799</v>
+        <v>4478</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C116" s="4">
-        <v>218.01</v>
+        <v>2100</v>
       </c>
       <c r="D116" s="2">
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>4848</v>
+        <v>4479</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C117" s="4">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D117" s="2">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>5022</v>
+        <v>4729</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C118" s="4">
-        <v>25</v>
+        <v>318.8</v>
       </c>
       <c r="D118" s="2">
         <v>9</v>
@@ -3069,13 +3078,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>5087</v>
+        <v>4730</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="C119" s="4">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="D119" s="2">
         <v>9</v>
@@ -3086,27 +3095,27 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>5117</v>
+        <v>4799</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C120" s="4">
-        <v>38</v>
+        <v>218.01</v>
       </c>
       <c r="D120" s="2">
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>5120</v>
+        <v>4848</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="C121" s="4">
         <v>25</v>
@@ -3115,35 +3124,35 @@
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>5187</v>
+        <v>5022</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C122" s="4">
-        <v>190</v>
+        <v>25</v>
       </c>
       <c r="D122" s="2">
         <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>5260</v>
+        <v>5087</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="C123" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D123" s="2">
         <v>9</v>
@@ -3154,13 +3163,13 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>5373</v>
+        <v>5117</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C124" s="4">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D124" s="2">
         <v>9</v>
@@ -3171,64 +3180,64 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>5736</v>
+        <v>5120</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="C125" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D125" s="2">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>5741</v>
+        <v>5187</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C126" s="4">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="D126" s="2">
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>5742</v>
+        <v>5260</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C127" s="4">
-        <v>19.2</v>
+        <v>5</v>
       </c>
       <c r="D127" s="2">
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>5743</v>
+        <v>5373</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C128" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D128" s="2">
         <v>9</v>
@@ -3239,302 +3248,302 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>5747</v>
+        <v>5736</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C129" s="4">
-        <v>5.98</v>
+        <v>5</v>
       </c>
       <c r="D129" s="2">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>5748</v>
+        <v>5741</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C130" s="4">
-        <v>4.5999999999999996</v>
+        <v>5</v>
       </c>
       <c r="D130" s="2">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>185</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>5750</v>
+        <v>5742</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C131" s="4">
-        <v>28.7</v>
+        <v>19.2</v>
       </c>
       <c r="D131" s="2">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>5796</v>
+        <v>5743</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C132" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D132" s="2">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>5796</v>
+        <v>5747</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C133" s="4">
-        <v>150</v>
+        <v>5.98</v>
       </c>
       <c r="D133" s="2">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>5797</v>
+        <v>5748</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C134" s="4">
-        <v>100</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D134" s="2">
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>5797</v>
+        <v>5750</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C135" s="4">
-        <v>900</v>
+        <v>28.7</v>
       </c>
       <c r="D135" s="2">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>5809</v>
+        <v>5796</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C136" s="4">
-        <v>359.4</v>
+        <v>50</v>
       </c>
       <c r="D136" s="2">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>5810</v>
+        <v>5796</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C137" s="4">
-        <v>1260</v>
+        <v>150</v>
       </c>
       <c r="D137" s="2">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>5811</v>
+        <v>5797</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C138" s="4">
-        <v>160.30000000000001</v>
+        <v>100</v>
       </c>
       <c r="D138" s="2">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>5812</v>
+        <v>5797</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C139" s="4">
-        <v>159.80000000000001</v>
+        <v>300</v>
       </c>
       <c r="D139" s="2">
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>5856</v>
+        <v>5797</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C140" s="4">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="D140" s="2">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>6505</v>
+        <v>5809</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C141" s="4">
-        <v>50</v>
+        <v>359.4</v>
       </c>
       <c r="D141" s="2">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>6505</v>
+        <v>5810</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C142" s="4">
-        <v>100</v>
+        <v>1260</v>
       </c>
       <c r="D142" s="2">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>6506</v>
+        <v>5811</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C143" s="4">
-        <v>450</v>
+        <v>160.30000000000001</v>
       </c>
       <c r="D143" s="2">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>6506</v>
+        <v>5812</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C144" s="4">
-        <v>650</v>
+        <v>159.80000000000001</v>
       </c>
       <c r="D144" s="2">
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>6507</v>
+        <v>5856</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C145" s="4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D145" s="2">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>6507</v>
+        <v>6505</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C146" s="4">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="D146" s="2">
         <v>9</v>
@@ -3545,13 +3554,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>6508</v>
+        <v>6505</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C147" s="4">
-        <v>14.9</v>
+        <v>100</v>
       </c>
       <c r="D147" s="2">
         <v>9</v>
@@ -3562,10 +3571,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>6508</v>
+        <v>6506</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C148" s="4">
         <v>150</v>
@@ -3579,13 +3588,13 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>6509</v>
+        <v>6506</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C149" s="4">
-        <v>82.8</v>
+        <v>300</v>
       </c>
       <c r="D149" s="2">
         <v>9</v>
@@ -3596,13 +3605,13 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>6510</v>
+        <v>6506</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C150" s="4">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="D150" s="2">
         <v>9</v>
@@ -3613,10 +3622,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>6510</v>
+        <v>6507</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C151" s="4">
         <v>100</v>
@@ -3630,13 +3639,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>6511</v>
+        <v>6507</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C152" s="4">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D152" s="2">
         <v>9</v>
@@ -3647,13 +3656,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>6512</v>
+        <v>6508</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C153" s="4">
-        <v>24.998999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="D153" s="2">
         <v>9</v>
@@ -3664,13 +3673,13 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>6514</v>
+        <v>6508</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C154" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D154" s="2">
         <v>9</v>
@@ -3681,13 +3690,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>6514</v>
+        <v>6509</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C155" s="4">
-        <v>250</v>
+        <v>82.8</v>
       </c>
       <c r="D155" s="2">
         <v>9</v>
@@ -3698,285 +3707,285 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>6828</v>
+        <v>6510</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C156" s="4">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D156" s="2">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>8329</v>
+        <v>6510</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C157" s="4">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="D157" s="2">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>8894</v>
+        <v>6511</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C158" s="4">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="D158" s="2">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>8895</v>
+        <v>6512</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C159" s="4">
-        <v>36.6</v>
+        <v>24.998999999999999</v>
       </c>
       <c r="D159" s="2">
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>8930</v>
+        <v>6514</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C160" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D160" s="2">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>9716</v>
+        <v>6514</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C161" s="4">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="D161" s="2">
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>9716</v>
+        <v>6828</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C162" s="4">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="D162" s="2">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>10497</v>
+        <v>8329</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C163" s="4">
-        <v>950</v>
+        <v>2850</v>
       </c>
       <c r="D163" s="2">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>185</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>10907</v>
+        <v>8894</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C164" s="4">
-        <v>2</v>
+        <v>540</v>
       </c>
       <c r="D164" s="2">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>11259</v>
+        <v>8895</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C165" s="4">
-        <v>25</v>
+        <v>36.6</v>
       </c>
       <c r="D165" s="2">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>11370</v>
+        <v>8930</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C166" s="4">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="D166" s="2">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>11370</v>
+        <v>9716</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C167" s="4">
-        <v>2340</v>
+        <v>18</v>
       </c>
       <c r="D167" s="2">
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>11370</v>
+        <v>9716</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C168" s="4">
-        <v>2700</v>
+        <v>36</v>
       </c>
       <c r="D168" s="2">
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>11371</v>
+        <v>10497</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C169" s="4">
-        <v>897</v>
+        <v>2470</v>
       </c>
       <c r="D169" s="2">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>11372</v>
+        <v>10907</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C170" s="4">
-        <v>540</v>
+        <v>2</v>
       </c>
       <c r="D170" s="2">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>11373</v>
+        <v>11259</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C171" s="4">
-        <v>705</v>
+        <v>25</v>
       </c>
       <c r="D171" s="2">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>11374</v>
+        <v>11370</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="C172" s="4">
-        <v>1800</v>
+        <v>4680</v>
       </c>
       <c r="D172" s="2">
         <v>9</v>
@@ -3987,13 +3996,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>11377</v>
+        <v>11371</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C173" s="4">
-        <v>300</v>
+        <v>897</v>
       </c>
       <c r="D173" s="2">
         <v>9</v>
@@ -4004,13 +4013,13 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>11377</v>
+        <v>11372</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C174" s="4">
-        <v>2700</v>
+        <v>540</v>
       </c>
       <c r="D174" s="2">
         <v>9</v>
@@ -4021,13 +4030,13 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>11378</v>
+        <v>11373</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C175" s="4">
-        <v>180</v>
+        <v>705</v>
       </c>
       <c r="D175" s="2">
         <v>9</v>
@@ -4038,13 +4047,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>11379</v>
+        <v>11374</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="C176" s="4">
-        <v>1260</v>
+        <v>1800</v>
       </c>
       <c r="D176" s="2">
         <v>9</v>
@@ -4055,13 +4064,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>11380</v>
+        <v>11377</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C177" s="4">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="D177" s="2">
         <v>9</v>
@@ -4072,47 +4081,47 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>11612</v>
+        <v>11377</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C178" s="4">
-        <v>25</v>
+        <v>2700</v>
       </c>
       <c r="D178" s="2">
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>11849</v>
+        <v>11378</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C179" s="4">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="D179" s="2">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>12710</v>
+        <v>11379</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C180" s="4">
-        <v>2.5</v>
+        <v>1260</v>
       </c>
       <c r="D180" s="2">
         <v>9</v>
@@ -4123,13 +4132,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>12711</v>
+        <v>11380</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C181" s="4">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="D181" s="2">
         <v>9</v>
@@ -4140,64 +4149,64 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>12712</v>
+        <v>11612</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C182" s="4">
-        <v>0.06</v>
+        <v>25</v>
       </c>
       <c r="D182" s="2">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>12713</v>
+        <v>11849</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C183" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D183" s="2">
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>12714</v>
+        <v>12710</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C184" s="4">
-        <v>0.05</v>
+        <v>2.5</v>
       </c>
       <c r="D184" s="2">
         <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>12715</v>
+        <v>12711</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C185" s="4">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="D185" s="2">
         <v>9</v>
@@ -4208,13 +4217,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>12716</v>
+        <v>12712</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C186" s="4">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="D186" s="2">
         <v>9</v>
@@ -4225,13 +4234,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>12717</v>
+        <v>12713</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C187" s="4">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="D187" s="2">
         <v>9</v>
@@ -4242,132 +4251,132 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>12718</v>
+        <v>12714</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C188" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D188" s="2">
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>12924</v>
+        <v>12715</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C189" s="4">
-        <v>20</v>
+        <v>0.05</v>
       </c>
       <c r="D189" s="2">
         <v>9</v>
       </c>
       <c r="E189" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>14753</v>
+        <v>12716</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C190" s="4">
-        <v>711</v>
+        <v>0.05</v>
       </c>
       <c r="D190" s="2">
         <v>9</v>
       </c>
       <c r="E190" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>15176</v>
+        <v>12717</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C191" s="4">
-        <v>150</v>
+        <v>0.05</v>
       </c>
       <c r="D191" s="2">
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>15178</v>
+        <v>12718</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C192" s="4">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="D192" s="2">
         <v>9</v>
       </c>
       <c r="E192" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>15180</v>
+        <v>12924</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C193" s="4">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="D193" s="2">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>15181</v>
+        <v>14753</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C194" s="4">
-        <v>210</v>
+        <v>711</v>
       </c>
       <c r="D194" s="2">
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>15182</v>
+        <v>15176</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C195" s="4">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="D195" s="2">
         <v>9</v>
@@ -4378,13 +4387,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>15183</v>
+        <v>15178</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C196" s="4">
-        <v>1540</v>
+        <v>150</v>
       </c>
       <c r="D196" s="2">
         <v>9</v>
@@ -4395,13 +4404,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>15184</v>
+        <v>15180</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C197" s="4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D197" s="2">
         <v>9</v>
@@ -4412,13 +4421,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>15185</v>
+        <v>15181</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C198" s="4">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="D198" s="2">
         <v>9</v>
@@ -4429,13 +4438,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>15187</v>
+        <v>15182</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C199" s="4">
-        <v>41.5</v>
+        <v>210</v>
       </c>
       <c r="D199" s="2">
         <v>9</v>
@@ -4446,13 +4455,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>15187</v>
+        <v>15183</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C200" s="4">
-        <v>125</v>
+        <v>1540</v>
       </c>
       <c r="D200" s="2">
         <v>9</v>
@@ -4463,94 +4472,156 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>16336</v>
+        <v>15184</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C201" s="4">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D201" s="2">
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>16336</v>
+        <v>15185</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C202" s="4">
-        <v>3060</v>
+        <v>50</v>
       </c>
       <c r="D202" s="2">
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
-        <v>16684</v>
+        <v>15187</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C203" s="4">
-        <v>360</v>
+        <v>41.5</v>
       </c>
       <c r="D203" s="2">
         <v>9</v>
       </c>
       <c r="E203" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
-        <v>16684</v>
+        <v>15187</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C204" s="4">
-        <v>2340</v>
+        <v>125</v>
       </c>
       <c r="D204" s="2">
         <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
+        <v>16336</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C205" s="4">
+        <v>180</v>
+      </c>
+      <c r="D205" s="2">
+        <v>9</v>
+      </c>
+      <c r="E205" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="2">
+        <v>16336</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C206" s="4">
+        <v>3060</v>
+      </c>
+      <c r="D206" s="2">
+        <v>9</v>
+      </c>
+      <c r="E206" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="2">
+        <v>16684</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C207" s="4">
+        <v>180</v>
+      </c>
+      <c r="D207" s="2">
+        <v>9</v>
+      </c>
+      <c r="E207" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="2">
+        <v>16684</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C208" s="4">
+        <v>2340</v>
+      </c>
+      <c r="D208" s="2">
+        <v>9</v>
+      </c>
+      <c r="E208" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="2">
         <v>17930</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B209" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C205" s="4">
-        <v>680</v>
-      </c>
-      <c r="D205" s="2">
-        <v>9</v>
-      </c>
-      <c r="E205" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="2"/>
-      <c r="B206" s="3"/>
-      <c r="C206" s="4"/>
-      <c r="D206" s="3"/>
+      <c r="C209" s="4">
+        <v>510</v>
+      </c>
+      <c r="D209" s="2">
+        <v>9</v>
+      </c>
+      <c r="E209" t="s">
+        <v>185</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
